--- a/Översikt BORÅS.xlsx
+++ b/Översikt BORÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45471</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45671</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45210</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45435</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45943</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45187</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>45321</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>46042</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44624</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45204</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>45526</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44501</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45393</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44873</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>44721</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>45351</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45316</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>45944</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>45604</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44748</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>45275</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>45393</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>44546</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45629</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>46076</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>44691</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>44817</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>44750</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>45119</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>45153</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>44630</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>45140</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>45093</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>45700</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>45281</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>44476</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>45007</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>44949</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>45379</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>46052</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44589</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>45153</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>45846</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>45867</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>44873</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>45348</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>44824</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>45867</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>44544</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>44958</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>45510</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>45671</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>45267</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>45321</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>45240</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>45264</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>45943</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>44742</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>44750</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>46008</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>45054</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>45321</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>44879</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>45126</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>45321</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>46198</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>45260</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>45686</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>46259</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>45629</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>45793</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>45793</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>46280</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45826</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>45841</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>44873</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>45671</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>46104</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>44586</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>44656</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>44512</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>44468</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>44631</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>44617</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         <v>44683</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>44544</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>44488</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>44830</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>44817</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>44817</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>44538</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>44462</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>44734</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>44837</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44586</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>44873</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44538</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>44510</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>44511</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>44544</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>44887</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>44502</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>44475</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>44491</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>44463</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>44523</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>44511</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44606</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>44605</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>44845</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>44845</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>44845</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>44624</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>44467</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>44463</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>44769</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>44673</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>44753</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>44873</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>44565</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>44550</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>44882</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>44529</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>44642</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44505</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>44678</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>45678</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45268</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44489</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>44489</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>44515</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>44740</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>44609</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>45119</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>45561</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>44897</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>45110</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44958</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>44552</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>45294</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>44900</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>45050</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14077,7 +14077,7 @@
         <v>45050</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>45034</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>45054</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>45351</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>44728</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>45232</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>45510</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>45588</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>45119</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>45000</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>45099</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>45575</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>45197</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>45629</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>45650</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>44639</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>45240</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>45240</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>45749</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>45212</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>45015</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>45727</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>45462</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         <v>45666</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>44910</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         <v>44916</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>44889</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>45356</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16136,7 +16136,7 @@
         <v>45638</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>45462</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>45231</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>44804</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>45294</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>45271</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>45406</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>45225</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>45538</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>44980</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
         <v>45180</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>44897</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>45321</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>45208</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>45190</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>45126</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>44581</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>45119</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>45233</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         <v>45758</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>44858</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>45316</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17747,7 +17747,7 @@
         <v>45562</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17820,7 +17820,7 @@
         <v>45120</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>45120</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>45120</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>45258</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>45194</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>45412</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>45537</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>45525</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
         <v>44888</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45120</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>45120</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>44958</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>44993</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>45350</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>45629</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>45379</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>45264</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>45058</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>45155</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>44467</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>45097</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>45870</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>45646</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>45453</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45855</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>45611</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>44844</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>46147</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>45184</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>45510</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>44547</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>45104</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>45211</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>44630</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>45887</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>45688</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>45197</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>45210</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>44644</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>45888</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>45888</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>45888</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>45888</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>45819</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>45196</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>44656</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>45316</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>45316</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>45593</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45895</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>45202</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>45096</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>45805</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>45456</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45895</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>44914</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44571</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>45215</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45547</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>45842</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>45968</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>45855</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45098</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45953</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45343</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>45547</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>46141</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>45294</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22799,7 +22799,7 @@
         <v>45909</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>45909</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>46140</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>44987</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>44964</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>45646</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>45205</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>45196</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>45917</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23461,7 +23461,7 @@
         <v>45922</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>45922</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45925</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>45870</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>45924</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>45301</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45176</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>45925</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45308</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>45929</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>45685</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>45931</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>45931</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
         <v>45931</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>46136</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>45937</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         <v>45938</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>45053</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>45803</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24878,7 +24878,7 @@
         <v>44859</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24951,7 +24951,7 @@
         <v>44848</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25024,7 +25024,7 @@
         <v>45943</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45937</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>45273</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>45947</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>45947</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45935</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>44592</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>45315</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>46153</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>46153</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>44896</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>45952</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>46153</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>45953</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>45085</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>46153</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>45472</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45959</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>45412</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>45357</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>45951</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45961</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>44964</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>46153</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>45960</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>45961</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>46153</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>46113</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>45964</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>45546</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>45103</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>45224</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45762</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45264</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>45974</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45629</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>45629</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>45629</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>45119</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>46154</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>46154</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>45176</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45603</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>45982</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>45982</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>45985</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>45308</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>44958</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>45982</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>45770</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>45678</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>44941</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28884,7 +28884,7 @@
         <v>45989</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>45268</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>45988</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>45329</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>45992</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>45637</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>45337</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>44900</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>44825</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>45994</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>45994</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>45629</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>45996</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>45321</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29916,7 +29916,7 @@
         <v>45321</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>45120</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>45217</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30140,7 +30140,7 @@
         <v>44704</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30213,7 +30213,7 @@
         <v>44897</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30286,7 +30286,7 @@
         <v>44652</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>46008</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>45546</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>46008</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30578,7 +30578,7 @@
         <v>45204</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30651,7 +30651,7 @@
         <v>45772</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>45715</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>45688</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
         <v>45688</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45713</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>45698</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>45701</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>45699</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>45615</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>45050</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>44839</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>45120</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>44959</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31600,7 +31600,7 @@
         <v>45162</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31673,7 +31673,7 @@
         <v>44964</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>44639</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>45212</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>45239</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>45538</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>46035</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>46037</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>46036</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>46036</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>44958</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>46037</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32476,7 +32476,7 @@
         <v>45148</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>46041</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>45015</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32695,7 +32695,7 @@
         <v>44546</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>45205</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>45917</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>46044</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>45845</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>45044</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33133,7 +33133,7 @@
         <v>45582</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33206,7 +33206,7 @@
         <v>45189</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33279,7 +33279,7 @@
         <v>46176</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33352,7 +33352,7 @@
         <v>45771</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>46175</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>45593</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>45548</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>46059</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>45756</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>45440</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>45670</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         <v>45058</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34014,7 +34014,7 @@
         <v>46182</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34087,7 +34087,7 @@
         <v>45474</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34160,7 +34160,7 @@
         <v>46076</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34233,7 +34233,7 @@
         <v>44866</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34306,7 +34306,7 @@
         <v>46076</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>46183</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>45240</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34530,7 +34530,7 @@
         <v>46183</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34608,7 +34608,7 @@
         <v>46183</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>46184</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34759,7 +34759,7 @@
         <v>46184</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>46084</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>46083</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>45817</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>45113</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>46085</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35197,7 +35197,7 @@
         <v>46188</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>45197</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>45186</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>45211</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35489,7 +35489,7 @@
         <v>46090</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35562,7 +35562,7 @@
         <v>46091</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>45477</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>46097</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35781,7 +35781,7 @@
         <v>45119</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>46099</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35927,7 +35927,7 @@
         <v>44866</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36000,7 +36000,7 @@
         <v>44886</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36073,7 +36073,7 @@
         <v>46099</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36146,7 +36146,7 @@
         <v>44771</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>44949</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36297,7 +36297,7 @@
         <v>44886</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36370,7 +36370,7 @@
         <v>44886</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>44854</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36516,7 +36516,7 @@
         <v>45225</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>46104</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36662,7 +36662,7 @@
         <v>46198</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>44875</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>46198</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>46105</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>46198</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37027,7 +37027,7 @@
         <v>46105</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>45126</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>45631</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>45321</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37324,7 +37324,7 @@
         <v>45120</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>45483</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>45483</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>46111</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>44995</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>46202</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45289</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37835,7 +37835,7 @@
         <v>46119</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>45545</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37981,7 +37981,7 @@
         <v>45769</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38054,7 +38054,7 @@
         <v>45579</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>46128</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>46183</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>46245</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45099</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>45579</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>46204</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>46132</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>46133</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38721,7 +38721,7 @@
         <v>44564</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45062</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>45062</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45611</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45670</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>44538</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>46204</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>46204</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>45798</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39383,7 +39383,7 @@
         <v>45863</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>46203</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39529,7 +39529,7 @@
         <v>46246</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>46246</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>46204</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>45364</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39821,7 +39821,7 @@
         <v>46203</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39894,7 +39894,7 @@
         <v>46251</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>46251</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45671</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>44577</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>45472</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>46206</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>46252</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>45636</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>45119</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45119</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40624,7 +40624,7 @@
         <v>45119</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>44916</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>45120</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40843,7 +40843,7 @@
         <v>45120</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40916,7 +40916,7 @@
         <v>45632</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>46253</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>44837</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41135,7 +41135,7 @@
         <v>45048</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>44746</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41281,7 +41281,7 @@
         <v>46254</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>46254</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41427,7 +41427,7 @@
         <v>45119</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>45516</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41573,7 +41573,7 @@
         <v>46216</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41646,7 +41646,7 @@
         <v>45216</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>44992</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41792,7 +41792,7 @@
         <v>45273</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>46216</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>45119</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45421</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>46260</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         <v>45194</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42230,7 +42230,7 @@
         <v>46217</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>46260</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>45119</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42449,7 +42449,7 @@
         <v>46260</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42522,7 +42522,7 @@
         <v>44748</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45302</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45432</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42751,7 +42751,7 @@
         <v>46260</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42824,7 +42824,7 @@
         <v>46260</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42897,7 +42897,7 @@
         <v>46260</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42970,7 +42970,7 @@
         <v>45216</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43043,7 +43043,7 @@
         <v>46260</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43116,7 +43116,7 @@
         <v>45321</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>44914</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43267,7 +43267,7 @@
         <v>45168</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45119</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>45741</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>46267</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>46267</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>46224</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43705,7 +43705,7 @@
         <v>45593</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45582</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43851,7 +43851,7 @@
         <v>46268</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>45294</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43997,7 +43997,7 @@
         <v>45308</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>46268</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44143,7 +44143,7 @@
         <v>45294</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>45294</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>45294</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44362,7 +44362,7 @@
         <v>45776</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44435,7 +44435,7 @@
         <v>45783</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>45782</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45783</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>45475</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>45587</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44800,7 +44800,7 @@
         <v>45209</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44873,7 +44873,7 @@
         <v>45721</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>45784</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>45596</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>46280</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45170,7 +45170,7 @@
         <v>45789</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45243,7 +45243,7 @@
         <v>45789</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45316,7 +45316,7 @@
         <v>46272</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45142</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45462,7 +45462,7 @@
         <v>45726</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45535,7 +45535,7 @@
         <v>45792</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45608,7 +45608,7 @@
         <v>46268</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>45798</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45759,7 +45759,7 @@
         <v>45803</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>45800</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>45803</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45978,7 +45978,7 @@
         <v>45803</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>45274</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45812</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46197,7 +46197,7 @@
         <v>44656</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46270,7 +46270,7 @@
         <v>45812</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46343,7 +46343,7 @@
         <v>45812</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46416,7 +46416,7 @@
         <v>45812</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46489,7 +46489,7 @@
         <v>45582</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46562,7 +46562,7 @@
         <v>45817</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46635,7 +46635,7 @@
         <v>45817</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46708,7 +46708,7 @@
         <v>45735</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>45819</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46854,7 +46854,7 @@
         <v>45821</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45821</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47000,7 +47000,7 @@
         <v>45472</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>45823</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>45727</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>45727</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47292,7 +47292,7 @@
         <v>45741</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47365,7 +47365,7 @@
         <v>45741</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47438,7 +47438,7 @@
         <v>45720</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47511,7 +47511,7 @@
         <v>45723</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47584,7 +47584,7 @@
         <v>45827</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47657,7 +47657,7 @@
         <v>45832</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47730,7 +47730,7 @@
         <v>45832</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47803,7 +47803,7 @@
         <v>45839</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47876,7 +47876,7 @@
         <v>45839</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47949,7 +47949,7 @@
         <v>45836</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45836</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48095,7 +48095,7 @@
         <v>45841</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48168,7 +48168,7 @@
         <v>45392</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         <v>45846</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>45848</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48387,7 +48387,7 @@
         <v>45392</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48460,7 +48460,7 @@
         <v>45866</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48533,7 +48533,7 @@
         <v>44882</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48606,7 +48606,7 @@
         <v>45610</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48679,7 +48679,7 @@
         <v>45567</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48752,7 +48752,7 @@
         <v>45612</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48825,7 +48825,7 @@
         <v>45877</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48898,7 +48898,7 @@
         <v>44467</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48971,7 +48971,7 @@
         <v>45174</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>44785</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>45008</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49190,7 +49190,7 @@
         <v>44624</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>44466</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49336,7 +49336,7 @@
         <v>44900</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49409,7 +49409,7 @@
         <v>44865</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49482,7 +49482,7 @@
         <v>45257</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>45173</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49628,7 +49628,7 @@
         <v>44642</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49701,7 +49701,7 @@
         <v>44900</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>45513</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
         <v>44706</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49925,7 +49925,7 @@
         <v>45173</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49998,7 +49998,7 @@
         <v>44900</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50071,7 +50071,7 @@
         <v>45534</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>44468</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50217,7 +50217,7 @@
         <v>45814</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50290,7 +50290,7 @@
         <v>45429</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50363,7 +50363,7 @@
         <v>45831</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50436,7 +50436,7 @@
         <v>45890</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50509,7 +50509,7 @@
         <v>45979</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>45740</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50655,7 +50655,7 @@
         <v>45740</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50728,7 +50728,7 @@
         <v>45127</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50801,7 +50801,7 @@
         <v>46073</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50874,7 +50874,7 @@
         <v>46083</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>

--- a/Översikt BORÅS.xlsx
+++ b/Översikt BORÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45471</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45210</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45671</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45435</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45943</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45187</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>46042</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45321</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44624</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>44501</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>45526</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>45393</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>45204</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44873</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>44721</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>45604</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>45944</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44748</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>44546</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>45275</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>45351</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>45393</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>46076</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>45316</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>45629</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>44691</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>44817</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>44476</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>45140</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>44630</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45119</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45093</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>44589</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>45153</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>45846</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>45867</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>45379</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>46052</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>45153</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>44750</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45281</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>45007</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>44949</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>44873</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45348</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>44824</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>45867</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>44544</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44879</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>44958</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>45793</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>45793</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>45054</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>45943</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>44750</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>46008</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>45321</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>45826</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>45841</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>45321</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>46198</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>45126</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>45321</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>45267</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>45671</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>46259</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>45240</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>46280</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>45264</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>45260</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>45510</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>44742</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45686</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>45629</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>44873</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>45671</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>46104</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>44586</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>44512</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>44656</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         <v>44468</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>44631</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>44617</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>44683</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>44544</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>44488</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>44830</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>44817</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>44817</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>44538</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>44734</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>44837</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>44586</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>44873</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>44538</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44510</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44511</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>44544</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>44887</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>44502</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>44475</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>44491</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>44523</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>44511</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>44606</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>44605</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>44845</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>44845</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>44845</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>44624</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>44467</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>44769</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>44673</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>44753</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>44873</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>44565</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44550</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>44882</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>44529</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44642</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>44505</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>44678</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12575,7 +12575,7 @@
         <v>45194</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>45412</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>45406</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>45050</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44916</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>44958</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>45538</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>45379</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>45062</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>45474</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>45615</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>45701</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>45713</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>45715</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>45688</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>45699</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>44844</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>44837</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>45210</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>45273</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>44577</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>45546</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>45798</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45887</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>46035</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45646</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>45888</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>46036</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>46036</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>45888</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>45888</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>45888</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>46037</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>46037</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44964</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>46041</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>44900</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>44859</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>46044</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>44630</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>45321</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>45575</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>44858</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45909</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>45800</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>44888</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>45909</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>44987</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>45216</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>46059</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44639</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>45917</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>44552</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45922</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         <v>45922</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         <v>44964</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>45803</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>44581</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>45924</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>45803</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>45803</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>45104</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>45925</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>46076</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>46076</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>45212</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>44910</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>45929</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>45931</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>45678</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>45817</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>45931</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         <v>45931</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>45274</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>44941</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>46085</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>46084</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45579</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>45547</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>46091</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>46090</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>45937</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>45593</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>45938</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>44897</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>45582</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>46097</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>46099</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19054,7 +19054,7 @@
         <v>45803</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>46099</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>45943</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>45225</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>45937</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>44854</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>44748</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>44949</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>45812</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>45812</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>44866</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         <v>44886</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>44886</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>44886</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>44740</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>46105</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>45947</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>45947</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>46104</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>46105</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>45483</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44656</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>45952</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>45015</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>45483</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>46111</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45343</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>45456</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>45812</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>45953</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>45960</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>45959</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>44746</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>44958</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>45951</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>46119</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>45961</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>45961</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>45258</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>45356</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>45603</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44959</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>45812</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>45058</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>45611</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45974</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>45058</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45119</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>45817</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45817</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45638</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>46132</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44993</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>46128</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>45119</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>45119</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>45982</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>45103</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45982</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>45982</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>45985</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>45582</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>45988</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45629</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>45629</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>45629</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>45119</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>45582</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>45992</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>45204</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>45989</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>45120</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>45855</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24452,7 +24452,7 @@
         <v>45994</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>45994</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>45735</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24671,7 +24671,7 @@
         <v>45996</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24744,7 +24744,7 @@
         <v>45453</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>45477</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>44538</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45176</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45098</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>45225</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>46147</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>45863</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>45855</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45798</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45688</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45819</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>45510</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>45953</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>46008</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>46008</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>45819</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>45805</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45176</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>45842</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45547</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>45688</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>45472</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45870</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>45821</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45273</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45823</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>45113</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>45202</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45821</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>45870</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>44467</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>45968</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>45197</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>45053</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>45727</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>46140</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>45168</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>45723</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>45741</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>45741</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>45827</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>45727</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27888,7 +27888,7 @@
         <v>45294</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44571</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>46141</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>46136</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>45832</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>45085</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45538</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>45832</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>45044</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45935</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>46153</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>46153</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>44897</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>45646</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>46153</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>46153</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>45211</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>46153</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>45096</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>46153</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>46154</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>44896</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>45216</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>46154</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>46113</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>45110</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>45836</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29859,7 +29859,7 @@
         <v>45836</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>45771</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>45727</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30083,7 +30083,7 @@
         <v>45337</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30156,7 +30156,7 @@
         <v>45097</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>45770</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>45839</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>45839</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>45841</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30521,7 +30521,7 @@
         <v>44489</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30594,7 +30594,7 @@
         <v>44825</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30667,7 +30667,7 @@
         <v>45392</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>45846</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>45099</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30891,7 +30891,7 @@
         <v>44546</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         <v>45848</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31037,7 +31037,7 @@
         <v>45120</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>45120</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>45120</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>45120</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>45329</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>45271</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31475,7 +31475,7 @@
         <v>45772</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>45462</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>45392</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>45917</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31767,7 +31767,7 @@
         <v>45062</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>45845</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>45866</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31986,7 +31986,7 @@
         <v>45545</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>45294</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>44889</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>46175</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>46176</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>45120</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>45316</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>44882</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>46183</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>46183</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>45637</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>45612</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>46182</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>45610</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45593</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>46183</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45162</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>45611</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>46184</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>46184</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33466,7 +33466,7 @@
         <v>46188</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>45567</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>45562</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>44609</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45670</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>45155</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>44515</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>45119</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>45629</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45877</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>46198</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>45217</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>46198</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>45196</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44547</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>45357</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>45054</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45631</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>45671</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>44644</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>46198</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>45472</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>45579</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>46183</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>46203</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>46202</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35369,7 +35369,7 @@
         <v>45119</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>45432</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>44639</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>46203</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>45316</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45196</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35807,7 +35807,7 @@
         <v>44564</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>45190</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>46204</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>46204</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36099,7 +36099,7 @@
         <v>46204</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36172,7 +36172,7 @@
         <v>46204</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36245,7 +36245,7 @@
         <v>45351</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36318,7 +36318,7 @@
         <v>46206</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>46251</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45636</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>46252</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>46251</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>46254</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36756,7 +36756,7 @@
         <v>46253</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36829,7 +36829,7 @@
         <v>45231</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45205</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36975,7 +36975,7 @@
         <v>45212</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>46254</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>45629</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>45148</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>45099</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>45126</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>45119</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45119</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>45685</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>46217</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>46216</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37778,7 +37778,7 @@
         <v>46260</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>46216</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37924,7 +37924,7 @@
         <v>45516</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         <v>46260</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>46260</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         <v>45741</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38216,7 +38216,7 @@
         <v>46260</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>46260</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>46260</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>46260</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45264</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>45120</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         <v>45240</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45302</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38805,7 +38805,7 @@
         <v>44704</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>45749</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38951,7 +38951,7 @@
         <v>45239</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39024,7 +39024,7 @@
         <v>45315</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>45186</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45233</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         <v>45758</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45268</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39389,7 +39389,7 @@
         <v>45756</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45289</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>46267</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>44804</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>46268</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45308</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>46267</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>45294</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>45294</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>45294</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40119,7 +40119,7 @@
         <v>45321</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>44839</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>46268</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>46224</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45294</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>45321</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40567,7 +40567,7 @@
         <v>45316</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>45240</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>44916</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>45294</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40859,7 +40859,7 @@
         <v>44897</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>45321</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41010,7 +41010,7 @@
         <v>45189</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>45548</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>45588</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45197</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>45224</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>46272</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>45197</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>45180</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>44964</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41667,7 +41667,7 @@
         <v>45215</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>46280</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41818,7 +41818,7 @@
         <v>44875</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>45561</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>45462</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42037,7 +42037,7 @@
         <v>44914</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>45769</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>44900</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42256,7 +42256,7 @@
         <v>44489</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42329,7 +42329,7 @@
         <v>45015</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>44995</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>46268</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>46245</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>46287</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44592</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>45048</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42840,7 +42840,7 @@
         <v>45895</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>46133</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42986,7 +42986,7 @@
         <v>45301</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43059,7 +43059,7 @@
         <v>45792</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43132,7 +43132,7 @@
         <v>44771</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43210,7 +43210,7 @@
         <v>45546</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>45593</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>45308</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43434,7 +43434,7 @@
         <v>44656</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>45308</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>45350</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>46246</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>46246</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>45670</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43877,7 +43877,7 @@
         <v>46289</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43950,7 +43950,7 @@
         <v>45720</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>46083</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44096,7 +44096,7 @@
         <v>45964</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>46289</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45510</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>44958</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>44652</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45678</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         <v>44992</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45120</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>45120</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>45364</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45000</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>44848</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>45472</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>45525</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>45050</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>45050</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45264</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45120</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>45650</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45488,7 +45488,7 @@
         <v>44958</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>45119</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>45184</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45707,7 +45707,7 @@
         <v>45666</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45785,7 +45785,7 @@
         <v>45421</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>44728</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>45126</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45194</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45629</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46150,7 +46150,7 @@
         <v>45119</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46223,7 +46223,7 @@
         <v>45119</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46296,7 +46296,7 @@
         <v>44866</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46369,7 +46369,7 @@
         <v>45232</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>45537</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46515,7 +46515,7 @@
         <v>45412</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46588,7 +46588,7 @@
         <v>45440</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>45205</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45240</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>44980</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45034</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>44914</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47026,7 +47026,7 @@
         <v>45268</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>45211</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>45321</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>45208</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45762</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>45119</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45632</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>45776</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>45782</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45475</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45587</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45784</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>45783</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45783</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>45596</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48131,7 +48131,7 @@
         <v>45721</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>45209</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45789</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>45789</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48423,7 +48423,7 @@
         <v>45726</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45142</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>44624</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>44642</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48715,7 +48715,7 @@
         <v>45513</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48788,7 +48788,7 @@
         <v>44706</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>44467</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>45174</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>44785</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49085,7 +49085,7 @@
         <v>45008</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>44466</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>44900</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>44865</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45257</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49450,7 +49450,7 @@
         <v>45173</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49523,7 +49523,7 @@
         <v>44900</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49596,7 +49596,7 @@
         <v>45173</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>44900</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>45534</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>44468</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>45814</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45429</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>45831</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>45890</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50180,7 +50180,7 @@
         <v>45979</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>45740</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>45740</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>45127</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50472,7 +50472,7 @@
         <v>46073</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50545,7 +50545,7 @@
         <v>46083</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>

--- a/Översikt BORÅS.xlsx
+++ b/Översikt BORÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45471</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45210</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45671</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45435</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45943</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45187</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>46042</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45321</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44624</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>44501</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>45526</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>45393</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>45204</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44873</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>44721</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>45604</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>45944</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44748</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>44546</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>45275</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>45351</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>45393</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>46076</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>45316</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>45629</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>44691</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>44817</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>44476</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>45140</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>44630</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45119</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45093</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>44589</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>45153</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>45846</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>45867</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>45379</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>46052</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>45153</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>44750</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45281</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>45007</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>44949</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>44873</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45348</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>44824</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>45867</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>44544</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44879</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>44958</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>45793</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>45793</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>45054</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>45943</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>44750</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>46008</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>45321</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>45826</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>45841</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>45321</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>46198</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>45126</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>45321</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>45267</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>45671</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>46259</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>45240</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>46280</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>45264</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>45260</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>45510</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>44742</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45686</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>45629</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>44873</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>45671</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>46104</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>44586</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>44512</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>44656</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         <v>44468</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>44631</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>44617</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>44683</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>44544</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>44488</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>44830</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>44817</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>44817</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>44538</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>44734</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>44837</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>44586</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>44873</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>44538</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44510</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44511</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>44544</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>44887</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>44502</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>44475</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>44491</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>44523</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>44511</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>44606</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>44605</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>44845</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>44845</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>44845</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>44624</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>44467</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>44769</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>44673</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>44753</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>44873</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>44565</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44550</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>44882</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>44529</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44642</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>44505</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>44678</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12575,7 +12575,7 @@
         <v>45194</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>45412</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>45406</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>45050</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44916</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>44958</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>45538</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>45379</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>45062</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>45474</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>45615</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>45701</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>45713</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>45715</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>45688</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>45699</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>44844</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>44837</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>45210</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>45273</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>44577</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>45546</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>45798</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45887</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>46035</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45646</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>45888</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>46036</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>46036</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>45888</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>45888</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>45888</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>46037</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>46037</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44964</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>46041</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>44900</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>44859</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>46044</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>44630</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>45321</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>45575</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>44858</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45909</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>45800</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>44888</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>45909</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>44987</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>45216</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>46059</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44639</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>45917</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>44552</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45922</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         <v>45922</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         <v>44964</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>45803</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>44581</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>45924</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>45803</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>45803</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>45104</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>45925</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>46076</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>46076</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>45212</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>44910</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>45929</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>45931</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>45678</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>45817</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>45931</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         <v>45931</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>45274</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>44941</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>46085</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>46084</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45579</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>45547</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>46091</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>46090</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>45937</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>45593</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>45938</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>44897</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>45582</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>46097</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>46099</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19054,7 +19054,7 @@
         <v>45803</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>46099</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>45943</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>45225</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>45937</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>44854</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>44748</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>44949</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>45812</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>45812</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>44866</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         <v>44886</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>44886</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>44886</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>44740</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>46105</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>45947</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>45947</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>46104</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>46105</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>45483</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>44656</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>45952</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>45015</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>45483</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>46111</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45343</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>45456</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>45812</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>45953</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>45960</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>45959</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>44746</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>44958</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>45951</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>46119</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>45961</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>45961</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>45258</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>45356</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>45603</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44959</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>45812</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>45058</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>45611</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22364,7 +22364,7 @@
         <v>45974</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>45058</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45119</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>45817</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45817</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45638</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>46132</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44993</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>46128</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>45119</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>45119</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>45982</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>45103</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45982</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>45982</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>45985</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>45582</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>45988</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45629</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>45629</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>45629</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>45119</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>45582</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>45992</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>45204</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>45989</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>45120</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>45855</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24452,7 +24452,7 @@
         <v>45994</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>45994</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>45735</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24671,7 +24671,7 @@
         <v>45996</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24744,7 +24744,7 @@
         <v>45453</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>45477</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>44538</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45176</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45098</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>45225</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>46147</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>45863</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>45855</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45798</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45688</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45819</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>45510</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>45953</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>46008</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>46008</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>45819</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>45805</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45176</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>45842</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45547</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>45688</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>45472</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45870</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>45821</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45273</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45823</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>45113</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>45202</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45821</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>45870</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>44467</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>45968</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>45197</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>45053</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>45727</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>46140</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>45168</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>45723</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>45741</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>45741</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>45827</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>45727</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27888,7 +27888,7 @@
         <v>45294</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44571</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>46141</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>46136</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>45832</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>45085</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45538</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>45832</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>45044</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45935</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>46153</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>46153</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>44897</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>45646</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>46153</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>46153</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>45211</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>46153</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>45096</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>46153</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>46154</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>44896</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>45216</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>46154</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>46113</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>45110</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>45836</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29859,7 +29859,7 @@
         <v>45836</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>45771</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>45727</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30083,7 +30083,7 @@
         <v>45337</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30156,7 +30156,7 @@
         <v>45097</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>45770</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>45839</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>45839</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>45841</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30521,7 +30521,7 @@
         <v>44489</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30594,7 +30594,7 @@
         <v>44825</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30667,7 +30667,7 @@
         <v>45392</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>45846</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>45099</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30891,7 +30891,7 @@
         <v>44546</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         <v>45848</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31037,7 +31037,7 @@
         <v>45120</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>45120</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>45120</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>45120</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>45329</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>45271</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31475,7 +31475,7 @@
         <v>45772</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>45462</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>45392</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>45917</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31767,7 +31767,7 @@
         <v>45062</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>45845</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>45866</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31986,7 +31986,7 @@
         <v>45545</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>45294</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>44889</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>46175</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>46176</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>45120</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>45316</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>44882</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>46183</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>46183</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>45637</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>45612</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>46182</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>45610</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45593</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>46183</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45162</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>45611</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>46184</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>46184</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33466,7 +33466,7 @@
         <v>46188</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>45567</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>45562</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>44609</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45670</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>45155</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>44515</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>45119</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>45629</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45877</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>46198</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>45217</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>46198</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>45196</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>44547</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>45357</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>45054</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45631</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>45671</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>44644</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>46198</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>45472</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>45579</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>46183</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>46203</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>46202</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35369,7 +35369,7 @@
         <v>45119</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
         <v>45432</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>44639</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>46203</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>45316</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45196</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35807,7 +35807,7 @@
         <v>44564</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>45190</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>46204</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>46204</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36099,7 +36099,7 @@
         <v>46204</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36172,7 +36172,7 @@
         <v>46204</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36245,7 +36245,7 @@
         <v>45351</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36318,7 +36318,7 @@
         <v>46206</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         <v>46251</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45636</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>46252</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>46251</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>46254</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36756,7 +36756,7 @@
         <v>46253</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36829,7 +36829,7 @@
         <v>45231</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45205</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36975,7 +36975,7 @@
         <v>45212</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>46254</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>45629</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>45148</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>45099</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>45126</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>45119</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>45119</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>45685</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>46217</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>46216</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37778,7 +37778,7 @@
         <v>46260</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>46216</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37924,7 +37924,7 @@
         <v>45516</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37997,7 +37997,7 @@
         <v>46260</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>46260</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         <v>45741</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38216,7 +38216,7 @@
         <v>46260</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>46260</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>46260</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>46260</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45264</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>45120</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         <v>45240</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45302</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38805,7 +38805,7 @@
         <v>44704</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>45749</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38951,7 +38951,7 @@
         <v>45239</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39024,7 +39024,7 @@
         <v>45315</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>45186</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45233</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         <v>45758</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45268</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39389,7 +39389,7 @@
         <v>45756</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45289</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>46267</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>44804</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>46268</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45308</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>46267</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>45294</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>45294</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>45294</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40119,7 +40119,7 @@
         <v>45321</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>44839</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>46268</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>46224</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45294</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>45321</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40567,7 +40567,7 @@
         <v>45316</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>45240</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>44916</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>45294</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40859,7 +40859,7 @@
         <v>44897</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>45321</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41010,7 +41010,7 @@
         <v>45189</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>45548</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>45588</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45197</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>45224</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>46272</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>45197</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>45180</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>44964</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41667,7 +41667,7 @@
         <v>45215</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>46280</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41818,7 +41818,7 @@
         <v>44875</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>45561</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>45462</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42037,7 +42037,7 @@
         <v>44914</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>45769</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>44900</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42256,7 +42256,7 @@
         <v>44489</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42329,7 +42329,7 @@
         <v>45015</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>44995</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>46268</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>46245</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>46287</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44592</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>45048</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42840,7 +42840,7 @@
         <v>45895</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>46133</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42986,7 +42986,7 @@
         <v>45301</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43059,7 +43059,7 @@
         <v>45792</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43132,7 +43132,7 @@
         <v>44771</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43210,7 +43210,7 @@
         <v>45546</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>45593</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>45308</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43434,7 +43434,7 @@
         <v>44656</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>45308</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>45350</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>46246</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>46246</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>45670</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43877,7 +43877,7 @@
         <v>46289</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43950,7 +43950,7 @@
         <v>45720</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>46083</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44096,7 +44096,7 @@
         <v>45964</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>46289</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45510</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>44958</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>44652</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45678</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         <v>44992</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45120</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>45120</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>45364</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45000</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>44848</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>45472</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>45525</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>45050</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>45050</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45264</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45120</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>45650</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45488,7 +45488,7 @@
         <v>44958</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>45119</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>45184</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45707,7 +45707,7 @@
         <v>45666</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45785,7 +45785,7 @@
         <v>45421</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>44728</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>45126</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45194</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45629</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46150,7 +46150,7 @@
         <v>45119</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46223,7 +46223,7 @@
         <v>45119</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46296,7 +46296,7 @@
         <v>44866</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46369,7 +46369,7 @@
         <v>45232</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>45537</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46515,7 +46515,7 @@
         <v>45412</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46588,7 +46588,7 @@
         <v>45440</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>45205</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45240</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>44980</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45034</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>44914</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47026,7 +47026,7 @@
         <v>45268</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>45211</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>45321</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>45208</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45762</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>45119</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45632</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>45776</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>45782</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45475</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45587</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45784</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>45783</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45783</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>45596</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48131,7 +48131,7 @@
         <v>45721</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>45209</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45789</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>45789</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48423,7 +48423,7 @@
         <v>45726</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45142</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>44624</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>44642</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48715,7 +48715,7 @@
         <v>45513</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48788,7 +48788,7 @@
         <v>44706</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>44467</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>45174</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49012,7 +49012,7 @@
         <v>44785</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49085,7 +49085,7 @@
         <v>45008</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>44466</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>44900</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>44865</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45257</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49450,7 +49450,7 @@
         <v>45173</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49523,7 +49523,7 @@
         <v>44900</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49596,7 +49596,7 @@
         <v>45173</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>44900</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>45534</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>44468</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>45814</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45429</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>45831</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>45890</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50180,7 +50180,7 @@
         <v>45979</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>45740</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>45740</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>45127</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50472,7 +50472,7 @@
         <v>46073</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50545,7 +50545,7 @@
         <v>46083</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>

--- a/Översikt BORÅS.xlsx
+++ b/Översikt BORÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45471</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45671</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45210</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45435</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45943</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45187</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>46042</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45321</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44624</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>44501</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>45204</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45526</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45393</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44873</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>44721</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>45351</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45604</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>45944</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45316</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>45982</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>45393</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>44748</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>46076</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45275</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>45629</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>44691</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>44817</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>44750</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>45119</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>45153</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>45140</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44630</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>45846</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>45867</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>45093</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>45281</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>45379</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>46052</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>44476</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>45007</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44949</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>44589</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>45153</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>44873</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45348</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>44824</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>45867</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>44544</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44958</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>45510</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>46008</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>45267</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>45793</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45793</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>45943</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>45671</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>45826</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>45240</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45841</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>45321</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>45264</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44742</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>44750</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>46198</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>45054</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>46259</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>45321</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>44879</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>45126</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>46280</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>45321</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>45260</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45686</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>45629</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>44873</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>45671</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>46104</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>44586</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>44512</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>44656</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         <v>44631</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>44617</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>44683</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>44544</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>44488</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>44830</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>44817</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>44817</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>44538</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>44734</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>44837</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>44586</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>44873</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>44538</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>44510</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44511</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44544</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>44887</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>44502</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>44475</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>44491</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>44523</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>44511</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>44606</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>44605</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>44845</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>44845</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>44845</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>44624</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>44769</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>44673</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>44753</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>44873</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>44565</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>44550</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>44882</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44529</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>44642</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>44505</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44678</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>45678</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>44609</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>44489</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>44489</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>45561</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>45268</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>44515</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>45575</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>45119</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>44740</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>44897</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>44958</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>44552</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>45294</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>44900</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>45110</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>45034</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>45050</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>45050</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>45054</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>45232</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>45351</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>44728</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>45119</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45197</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45588</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>45212</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45510</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>45000</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>45099</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>45789</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>45789</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>44639</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>45629</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>45650</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>45240</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>46008</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>45240</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>44844</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>46008</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>45749</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>45015</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>45727</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>45715</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>45142</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45688</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45688</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45726</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>45713</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>45462</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>45701</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>45699</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>45887</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>45615</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16381,7 +16381,7 @@
         <v>45888</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
         <v>45888</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>45888</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>45888</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>44910</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>44916</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>45666</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>44889</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>45638</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>46035</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>45462</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>45356</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>44804</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>46037</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>46036</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>46036</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>46037</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>46041</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>45231</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>45909</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>45909</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>44987</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45294</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>46044</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>45406</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45225</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45798</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>45803</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45800</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>45803</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>45803</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>45271</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>45917</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45922</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>45922</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>44980</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19039,7 +19039,7 @@
         <v>45924</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45180</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>45925</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45538</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>44897</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>45929</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>45931</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>46059</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>45931</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>45321</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>45208</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>45931</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>45190</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>45126</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>45758</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44581</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>45119</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>45233</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>45937</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>45938</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>45803</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>45943</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>45937</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>46076</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>44858</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>45562</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>46076</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>45316</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>45947</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>45947</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>45274</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>45120</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>45120</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45120</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>45258</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45194</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>46084</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>45817</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>45812</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>45412</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>45537</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
         <v>45953</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22140,7 +22140,7 @@
         <v>45525</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22213,7 +22213,7 @@
         <v>44656</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>46085</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>45812</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>45812</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>45959</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>45812</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>45951</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45961</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>45582</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44888</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>46090</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23026,7 +23026,7 @@
         <v>45960</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>45961</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>46091</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>45120</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45120</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>44958</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>45817</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>45350</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>46097</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>44993</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>46099</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44866</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44886</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>46099</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>44949</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>44886</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>44886</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>45097</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>44854</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>46104</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>45974</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>45817</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>45629</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>45735</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>45819</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24851,7 +24851,7 @@
         <v>45058</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>46105</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>46105</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>45379</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>45264</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>45483</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>45483</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25362,7 +25362,7 @@
         <v>46111</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>45821</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25508,7 +25508,7 @@
         <v>45982</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>45982</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>45985</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25737,7 +25737,7 @@
         <v>45821</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>45982</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>45155</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>45472</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>45823</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>46119</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>45989</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>45988</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>45992</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45727</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>45727</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45994</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>46128</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>45611</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>45994</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45741</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>45741</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>45184</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>45996</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>45510</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>45723</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>45827</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>44547</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>45104</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>45211</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>44630</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>45832</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>46132</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>45832</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27888,7 +27888,7 @@
         <v>45197</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44644</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>45196</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>44656</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>45316</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>45316</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45593</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>45202</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>45096</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45456</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>44914</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>45839</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>45839</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>45836</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44571</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>45836</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>45215</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44538</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29207,7 +29207,7 @@
         <v>45547</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>45798</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29353,7 +29353,7 @@
         <v>45863</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>45841</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>45392</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>45343</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45547</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>45870</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>45453</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>45855</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>45846</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>46147</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>45848</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>44964</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>45646</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45688</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45205</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>45819</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>45196</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>45805</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>45301</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30745,7 +30745,7 @@
         <v>45842</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30818,7 +30818,7 @@
         <v>45968</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30891,7 +30891,7 @@
         <v>45855</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         <v>45098</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31037,7 +31037,7 @@
         <v>45308</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>45685</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>45953</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>46141</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>45392</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>45294</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>46140</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31553,7 +31553,7 @@
         <v>45866</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
         <v>45053</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>44859</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31772,7 +31772,7 @@
         <v>44848</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31845,7 +31845,7 @@
         <v>45273</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>44882</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45870</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>45176</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>45610</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>44592</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>45315</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>44896</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>46136</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>45085</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>45567</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>45935</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32721,7 +32721,7 @@
         <v>45472</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>45612</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>46153</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>46153</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>45412</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>46153</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>45357</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>46153</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>44964</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>46153</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>46153</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>46113</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>46154</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>46154</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>45546</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>45103</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>45224</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>45762</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34040,7 +34040,7 @@
         <v>45337</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>45264</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>45629</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>45629</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>45629</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45119</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44825</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>45877</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>45176</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34697,7 +34697,7 @@
         <v>45603</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>45308</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>44958</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>45770</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34994,7 +34994,7 @@
         <v>45678</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>44941</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>45268</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35218,7 +35218,7 @@
         <v>45329</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>45917</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>45845</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>45637</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35510,7 +35510,7 @@
         <v>45646</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>46176</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35656,7 +35656,7 @@
         <v>46175</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>45210</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>44900</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>46182</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35948,7 +35948,7 @@
         <v>46183</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>46183</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>46183</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>46184</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45629</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>46184</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>46188</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>45321</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>45321</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>45120</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>45217</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>44704</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36849,7 +36849,7 @@
         <v>44897</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>44652</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45546</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         <v>45204</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37141,7 +37141,7 @@
         <v>45772</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>46198</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37287,7 +37287,7 @@
         <v>46198</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>46198</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>45050</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37506,7 +37506,7 @@
         <v>44839</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>46202</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>45120</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>44959</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>45162</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>44964</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>46183</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>44639</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38095,7 +38095,7 @@
         <v>46204</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38168,7 +38168,7 @@
         <v>45212</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45239</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38314,7 +38314,7 @@
         <v>45538</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38387,7 +38387,7 @@
         <v>46204</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38460,7 +38460,7 @@
         <v>46204</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38533,7 +38533,7 @@
         <v>46203</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38606,7 +38606,7 @@
         <v>46204</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38679,7 +38679,7 @@
         <v>46203</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38752,7 +38752,7 @@
         <v>46206</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38825,7 +38825,7 @@
         <v>44958</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38898,7 +38898,7 @@
         <v>45148</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
         <v>45015</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>44546</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>45205</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39190,7 +39190,7 @@
         <v>46216</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>45044</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>45582</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>46216</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>45189</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>46260</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>45771</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>46217</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>46260</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>46260</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45593</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>46260</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>46260</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>46260</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>45548</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>46260</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40358,7 +40358,7 @@
         <v>45756</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>45440</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>45670</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40577,7 +40577,7 @@
         <v>46267</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>45058</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>46267</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40796,7 +40796,7 @@
         <v>46224</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>46268</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40942,7 +40942,7 @@
         <v>45294</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41015,7 +41015,7 @@
         <v>45308</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>46268</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45474</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45294</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>45294</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45294</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>44866</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
         <v>45240</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>45113</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>46280</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>46272</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45197</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>45186</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>45211</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45477</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>46268</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>45119</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>44771</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>45792</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>45225</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>44875</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>45895</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>45126</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>45631</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>46133</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>45321</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45120</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>46287</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>44995</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>46289</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>46245</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>46246</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>46246</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>45289</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>45545</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>45769</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>46289</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45579</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>45099</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45964</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45579</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45720</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>46083</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>44564</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>45062</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>45062</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45611</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>46251</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         <v>46252</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45670</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>46295</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>46251</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45364</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>46254</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>46254</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>46253</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>45671</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>44577</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45472</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45636</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>45119</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45488,7 +45488,7 @@
         <v>45119</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>45119</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>44916</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45707,7 +45707,7 @@
         <v>45120</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45780,7 +45780,7 @@
         <v>45120</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45853,7 +45853,7 @@
         <v>45632</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>44837</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>45048</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46072,7 +46072,7 @@
         <v>44746</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>45119</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45516</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46291,7 +46291,7 @@
         <v>45216</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>44992</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>45273</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46510,7 +46510,7 @@
         <v>45119</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>45421</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45194</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>45119</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>44748</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45302</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>45432</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>45216</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>45321</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>44914</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>45168</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45119</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>45741</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45593</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>45582</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>45776</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45783</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45782</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45783</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>45475</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45587</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>45209</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48131,7 +48131,7 @@
         <v>45721</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>45784</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45596</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>45174</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48423,7 +48423,7 @@
         <v>44785</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45008</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>44624</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>44900</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48715,7 +48715,7 @@
         <v>44865</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48788,7 +48788,7 @@
         <v>45257</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>45173</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>44642</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49007,7 +49007,7 @@
         <v>44900</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49080,7 +49080,7 @@
         <v>45513</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>44706</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>45173</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>44900</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45534</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49450,7 +49450,7 @@
         <v>45814</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49523,7 +49523,7 @@
         <v>45429</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49596,7 +49596,7 @@
         <v>45831</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>45890</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>45979</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>45740</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>45740</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45127</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>46073</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>46083</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>

--- a/Översikt BORÅS.xlsx
+++ b/Översikt BORÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45471</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45671</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45210</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45435</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45943</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45187</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>46042</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45321</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44624</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>44501</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>45204</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45526</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45393</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44873</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>44721</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>45351</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45604</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>45944</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45316</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>45982</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>45393</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>44748</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>46076</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45275</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>45629</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>44691</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>44817</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>44750</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>45119</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>45153</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>45140</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44630</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>45846</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>45867</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>45093</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>45281</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>45379</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>46052</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>44476</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>45007</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44949</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>44589</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>45153</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>44873</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45348</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>44824</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>45867</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>44544</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44958</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>45510</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>46008</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>45267</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>45793</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45793</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>45943</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>45671</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>45826</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>45240</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45841</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>45321</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>45264</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44742</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>44750</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>46198</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>45054</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>46259</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>45321</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8196,7 +8196,7 @@
         <v>44879</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>45126</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>46280</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>45321</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>45260</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45686</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>45629</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>44873</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>45671</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>46104</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>44586</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>44512</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>44656</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         <v>44631</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>44617</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>44683</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>44544</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>44488</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>44830</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>44817</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>44817</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>44538</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>44734</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>44837</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>44586</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>44873</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>44538</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>44510</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44511</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44544</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>44887</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>44502</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>44475</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>44491</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>44523</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>44511</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>44606</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>44605</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>44845</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>44845</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>44845</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>44624</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>44769</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>44673</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>44753</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>44873</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>44565</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>44550</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>44882</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44529</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>44642</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>44505</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44678</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>45678</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>44609</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>44489</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>44489</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>45561</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>45268</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>44515</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>45575</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>45119</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>44740</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>44897</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>44958</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>44552</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>45294</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>44900</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>45110</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>45034</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>45050</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>45050</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>45054</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>45232</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>45351</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>44728</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>45119</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45197</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45588</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>45212</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45510</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>45000</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>45099</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>45789</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>45789</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>44639</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>45629</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>45650</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>45240</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>46008</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>45240</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>44844</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>46008</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>45749</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>45015</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>45727</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>45715</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>45142</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45688</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45688</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45726</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>45713</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>45462</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>45701</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>45699</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>45887</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>45615</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16381,7 +16381,7 @@
         <v>45888</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
         <v>45888</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>45888</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>45888</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>44910</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>44916</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>45666</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>44889</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>45638</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>46035</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>45462</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>45356</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>44804</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>46037</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>46036</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>46036</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>46037</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>46041</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>45231</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>45909</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>45909</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>44987</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45294</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>46044</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>45406</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45225</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45798</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>45803</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45800</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>45803</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>45803</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>45271</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>45917</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45922</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>45922</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>44980</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19039,7 +19039,7 @@
         <v>45924</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45180</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>45925</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45538</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>44897</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>45929</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>45931</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>46059</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>45931</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>45321</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>45208</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>45931</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>45190</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>45126</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>45758</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44581</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>45119</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>45233</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>45937</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>45938</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>45803</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>45943</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>45937</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>46076</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>44858</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>45562</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>46076</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>45316</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>45947</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>45947</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>45274</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>45120</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>45120</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45120</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>45258</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45194</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>46084</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>45817</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>45812</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>45412</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>45537</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
         <v>45953</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22140,7 +22140,7 @@
         <v>45525</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22213,7 +22213,7 @@
         <v>44656</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>46085</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>45812</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>45812</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>45959</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>45812</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>45951</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45961</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>45582</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44888</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>46090</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23026,7 +23026,7 @@
         <v>45960</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>45961</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>46091</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>45120</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45120</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>44958</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>45817</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>45350</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>46097</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>44993</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>46099</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44866</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44886</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>46099</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>44949</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>44886</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>44886</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>45097</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>44854</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>46104</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>45974</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>45817</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>45629</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24705,7 +24705,7 @@
         <v>45735</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24778,7 +24778,7 @@
         <v>45819</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24851,7 +24851,7 @@
         <v>45058</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>46105</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>46105</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>45379</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>45264</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>45483</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>45483</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25362,7 +25362,7 @@
         <v>46111</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>45821</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25508,7 +25508,7 @@
         <v>45982</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>45982</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>45985</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25737,7 +25737,7 @@
         <v>45821</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>45982</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>45155</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>45472</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>45823</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>46119</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>45989</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>45988</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>45992</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>45727</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>45727</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45994</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>46128</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>45611</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>45994</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45741</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>45741</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>45184</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>45996</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>45510</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>45723</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>45827</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>44547</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>45104</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>45211</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>44630</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>45832</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27742,7 +27742,7 @@
         <v>46132</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27815,7 +27815,7 @@
         <v>45832</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27888,7 +27888,7 @@
         <v>45197</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>44644</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>45196</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>44656</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>45316</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>45316</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45593</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>45202</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>45096</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45456</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>44914</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>45839</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>45839</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>45836</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44571</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>45836</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>45215</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44538</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29207,7 +29207,7 @@
         <v>45547</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>45798</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29353,7 +29353,7 @@
         <v>45863</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>45841</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>45392</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>45343</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>45547</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>45870</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>45453</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>45855</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>45846</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>46147</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>45848</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>44964</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>45646</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45688</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45205</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>45819</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>45196</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>45805</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>45301</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30745,7 +30745,7 @@
         <v>45842</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30818,7 +30818,7 @@
         <v>45968</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30891,7 +30891,7 @@
         <v>45855</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         <v>45098</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31037,7 +31037,7 @@
         <v>45308</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>45685</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>45953</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>46141</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>45392</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>45294</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>46140</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31553,7 +31553,7 @@
         <v>45866</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
         <v>45053</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>44859</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31772,7 +31772,7 @@
         <v>44848</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31845,7 +31845,7 @@
         <v>45273</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>44882</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45870</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>45176</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>45610</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>44592</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>45315</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>44896</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>46136</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>45085</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>45567</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>45935</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32721,7 +32721,7 @@
         <v>45472</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>45612</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>46153</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>46153</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>45412</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>46153</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>45357</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>46153</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>44964</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>46153</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>46153</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>46113</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>46154</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>46154</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>45546</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>45103</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>45224</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>45762</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34040,7 +34040,7 @@
         <v>45337</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>45264</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>45629</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>45629</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>45629</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45119</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>44825</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>45877</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>45176</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34697,7 +34697,7 @@
         <v>45603</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>45308</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>44958</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>45770</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34994,7 +34994,7 @@
         <v>45678</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>44941</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>45268</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35218,7 +35218,7 @@
         <v>45329</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>45917</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>45845</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>45637</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35510,7 +35510,7 @@
         <v>45646</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>46176</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35656,7 +35656,7 @@
         <v>46175</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>45210</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>44900</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>46182</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35948,7 +35948,7 @@
         <v>46183</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>46183</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>46183</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>46184</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45629</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>46184</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>46188</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>45321</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>45321</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>45120</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>45217</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>44704</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36849,7 +36849,7 @@
         <v>44897</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>44652</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45546</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         <v>45204</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37141,7 +37141,7 @@
         <v>45772</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>46198</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37287,7 +37287,7 @@
         <v>46198</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37360,7 +37360,7 @@
         <v>46198</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>45050</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37506,7 +37506,7 @@
         <v>44839</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37579,7 +37579,7 @@
         <v>46202</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>45120</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>44959</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>45162</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>44964</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>46183</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>44639</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38095,7 +38095,7 @@
         <v>46204</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38168,7 +38168,7 @@
         <v>45212</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45239</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38314,7 +38314,7 @@
         <v>45538</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38387,7 +38387,7 @@
         <v>46204</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38460,7 +38460,7 @@
         <v>46204</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38533,7 +38533,7 @@
         <v>46203</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38606,7 +38606,7 @@
         <v>46204</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38679,7 +38679,7 @@
         <v>46203</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38752,7 +38752,7 @@
         <v>46206</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38825,7 +38825,7 @@
         <v>44958</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38898,7 +38898,7 @@
         <v>45148</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
         <v>45015</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>44546</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>45205</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39190,7 +39190,7 @@
         <v>46216</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>45044</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>45582</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>46216</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>45189</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>46260</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>45771</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>46217</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>46260</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>46260</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45593</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>46260</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>46260</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>46260</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>45548</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>46260</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40358,7 +40358,7 @@
         <v>45756</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>45440</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>45670</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40577,7 +40577,7 @@
         <v>46267</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>45058</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>46267</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40796,7 +40796,7 @@
         <v>46224</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>46268</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40942,7 +40942,7 @@
         <v>45294</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41015,7 +41015,7 @@
         <v>45308</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>46268</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45474</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45294</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>45294</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45294</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>44866</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
         <v>45240</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>45113</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>46280</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>46272</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45197</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>45186</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>45211</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45477</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>46268</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>45119</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>44771</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>45792</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>45225</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>44875</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>45895</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>45126</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>45631</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>46133</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>45321</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45120</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>46287</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>44995</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>46289</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>46245</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>46246</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>46246</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>45289</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>45545</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>45769</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>46289</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45579</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>45099</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45964</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45579</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45720</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>46083</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>44564</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>45062</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>45062</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45611</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>46251</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         <v>46252</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45670</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>46295</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>46251</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>45364</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>46254</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>46254</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>46253</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>45671</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>44577</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45472</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45636</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>45119</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45488,7 +45488,7 @@
         <v>45119</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>45119</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>44916</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45707,7 +45707,7 @@
         <v>45120</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45780,7 +45780,7 @@
         <v>45120</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45853,7 +45853,7 @@
         <v>45632</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>44837</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>45048</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46072,7 +46072,7 @@
         <v>44746</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>45119</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>45516</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46291,7 +46291,7 @@
         <v>45216</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>44992</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>45273</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46510,7 +46510,7 @@
         <v>45119</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>45421</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45194</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>45119</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>44748</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46880,7 +46880,7 @@
         <v>45302</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>45432</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>45216</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>45321</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>44914</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>45168</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45119</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>45741</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45593</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>45582</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>45776</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45783</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45782</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45783</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>45475</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45587</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>45209</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48131,7 +48131,7 @@
         <v>45721</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>45784</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45596</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>45174</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48423,7 +48423,7 @@
         <v>44785</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45008</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>44624</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>44900</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48715,7 +48715,7 @@
         <v>44865</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48788,7 +48788,7 @@
         <v>45257</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>45173</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>44642</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49007,7 +49007,7 @@
         <v>44900</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49080,7 +49080,7 @@
         <v>45513</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>44706</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>45173</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>44900</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45534</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49450,7 +49450,7 @@
         <v>45814</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49523,7 +49523,7 @@
         <v>45429</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49596,7 +49596,7 @@
         <v>45831</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>45890</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>45979</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>45740</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>45740</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45127</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>46073</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>46083</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>

--- a/Översikt BORÅS.xlsx
+++ b/Översikt BORÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45471</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45671</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45210</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45435</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45187</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>45943</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>45321</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>46042</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44624</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45526</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>44501</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>45204</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45393</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44873</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>44721</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>45316</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45629</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>44546</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45275</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>45351</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>44748</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>45944</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>45982</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45604</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>45393</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>46076</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>44691</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>44817</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>44589</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45153</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>44949</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>44630</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>45140</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>45153</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45119</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>45846</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>45867</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>44750</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>45093</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>45281</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>45007</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>45379</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>46052</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>44873</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>45348</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>44824</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>45867</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>44544</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>44879</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>45321</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>44958</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>44742</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45267</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>45686</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45629</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>45126</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>45793</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>45793</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>45321</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>45671</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>44750</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>45943</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45826</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>45841</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>45240</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>45264</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>46008</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45260</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>45510</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>45321</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>46198</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>46280</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>46259</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>44873</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>45671</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>46104</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>44512</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>44586</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>44656</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         <v>44631</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>44617</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>44683</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>44544</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>44488</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>44830</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>44817</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44817</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>44538</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>44734</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>44837</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>44586</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>44873</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>44538</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>44510</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>44511</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>44544</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>44887</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>44502</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>44491</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>44523</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>44882</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>44529</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>44673</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>44753</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>44511</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         <v>44873</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>44769</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>44606</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         <v>44642</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>44565</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>44605</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>44845</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>44845</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>44845</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>44624</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>44505</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>44550</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>44678</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>45044</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>45406</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>45264</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>45120</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         <v>45650</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>44897</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>44958</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12647,7 +12647,7 @@
         <v>45646</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>45211</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>45096</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>45119</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>45412</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>45050</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>44896</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>45216</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>45110</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>45194</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>45184</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>45771</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>45666</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>45727</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>45421</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45097</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>44728</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45770</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>45126</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>45194</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>45629</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>45119</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>44916</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>44489</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>45119</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>44866</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>44958</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>45538</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>45232</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>45099</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>45537</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>44546</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>45412</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>45120</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>45120</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45120</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>45379</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>45120</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45062</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45440</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45205</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>45240</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44844</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>45474</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45329</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45210</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>44980</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>44837</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>45271</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>45772</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>45034</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>45462</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>45887</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>45273</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>45646</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>45062</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>45888</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>45888</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>45888</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>45888</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>45545</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>44577</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>45294</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>44914</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>45268</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>45546</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>45211</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>45321</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>45208</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>44889</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>45762</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45119</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45632</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>44964</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>44900</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>44859</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>45909</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45120</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>44630</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45321</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>45909</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>45776</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>44987</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>45316</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>45575</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>45782</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>44858</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>45637</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45475</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>45587</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>45593</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45784</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>45783</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>44888</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>45783</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>45596</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>45162</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45611</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45721</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45209</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45917</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>45216</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45922</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44639</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>45562</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>44609</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>45670</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45922</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>44552</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45155</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>44515</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45119</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>44964</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>45924</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>44581</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21097,7 +21097,7 @@
         <v>45789</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>45789</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21243,7 +21243,7 @@
         <v>45925</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21316,7 +21316,7 @@
         <v>45726</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45104</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>45629</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>45142</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>45217</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>45212</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>44910</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>45196</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>44547</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>45929</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>45357</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>45054</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>45931</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22270,7 +22270,7 @@
         <v>45678</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45631</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45671</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>44644</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>44941</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45472</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45579</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45931</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>45931</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>45798</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45579</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>45547</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>45119</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>45432</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>44639</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>45316</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>45593</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>44897</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>45196</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>44564</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         <v>45190</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45582</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>45800</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>45351</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>45803</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>45803</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>45803</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45225</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>45636</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44748</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>44740</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>45274</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45938</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>45812</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>45812</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>44656</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>45015</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>45812</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>45231</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45803</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>45943</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45937</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>45812</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>45205</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45212</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45343</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>45629</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>45817</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>45817</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>45456</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>45148</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         <v>45582</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26101,7 +26101,7 @@
         <v>45735</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26174,7 +26174,7 @@
         <v>44746</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26247,7 +26247,7 @@
         <v>44958</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>45819</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>45472</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>45258</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>45356</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26617,7 +26617,7 @@
         <v>45821</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26690,7 +26690,7 @@
         <v>45099</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>45823</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>45821</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>45947</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>45947</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>45603</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>45126</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>45119</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>45119</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>44959</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>45727</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>45685</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         <v>45723</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>45741</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>45741</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>45827</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>45727</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>45516</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>45058</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>45611</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>45832</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28223,7 +28223,7 @@
         <v>45832</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>45741</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>45953</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>45960</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>45959</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>45951</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>45961</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>45058</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>45119</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>45638</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>45961</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         <v>45836</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>45264</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>44993</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29250,7 +29250,7 @@
         <v>45836</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>45839</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>45120</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>45240</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>45119</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45119</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>45103</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29761,7 +29761,7 @@
         <v>45839</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>45841</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>45302</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>44704</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>45392</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45749</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>45629</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>45629</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>45629</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>45239</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>45119</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>45582</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>45846</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30715,7 +30715,7 @@
         <v>45204</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>45315</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30861,7 +30861,7 @@
         <v>45186</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>45233</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>45758</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>45268</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31153,7 +31153,7 @@
         <v>45974</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>45756</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>45120</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>45289</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>44804</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>45477</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>45392</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>45225</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31737,7 +31737,7 @@
         <v>45321</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>44839</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>45866</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>44882</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32034,7 +32034,7 @@
         <v>45612</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32107,7 +32107,7 @@
         <v>45321</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32185,7 +32185,7 @@
         <v>45510</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>45610</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>45316</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>45240</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44916</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>45567</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45176</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>45294</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>44897</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>45321</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>45877</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32993,7 +32993,7 @@
         <v>45982</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>45547</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33144,7 +33144,7 @@
         <v>45982</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45273</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>45113</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>45202</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>45189</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33538,7 +33538,7 @@
         <v>45548</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45982</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33689,7 +33689,7 @@
         <v>46099</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45588</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>46099</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>45197</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>45985</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>45224</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>44854</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34200,7 +34200,7 @@
         <v>45197</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>44949</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>44866</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>44886</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>44886</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>44886</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>45197</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34711,7 +34711,7 @@
         <v>45180</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>46105</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34857,7 +34857,7 @@
         <v>44964</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34930,7 +34930,7 @@
         <v>45215</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>45053</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35076,7 +35076,7 @@
         <v>46104</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>46105</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35222,7 +35222,7 @@
         <v>45168</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>45483</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35368,7 +35368,7 @@
         <v>44875</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>45561</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>45483</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35587,7 +35587,7 @@
         <v>45988</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35660,7 +35660,7 @@
         <v>45462</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35733,7 +35733,7 @@
         <v>46111</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35806,7 +35806,7 @@
         <v>44571</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35879,7 +35879,7 @@
         <v>45992</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35952,7 +35952,7 @@
         <v>45989</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>44914</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36103,7 +36103,7 @@
         <v>45769</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36176,7 +36176,7 @@
         <v>45085</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36249,7 +36249,7 @@
         <v>45538</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>44900</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>45994</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>45994</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>46119</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>44489</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45015</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>44995</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>45996</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>46132</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>46128</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>44592</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>45048</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37198,7 +37198,7 @@
         <v>45301</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44771</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         <v>45546</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37422,7 +37422,7 @@
         <v>45593</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>46008</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>46008</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>45308</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>44656</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37792,7 +37792,7 @@
         <v>45308</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>45350</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>45670</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38016,7 +38016,7 @@
         <v>45855</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>45688</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38162,7 +38162,7 @@
         <v>45615</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38235,7 +38235,7 @@
         <v>45701</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>45713</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38381,7 +38381,7 @@
         <v>45715</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>45688</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>45699</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38600,7 +38600,7 @@
         <v>45453</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>44538</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45176</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38824,7 +38824,7 @@
         <v>45098</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>46147</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45863</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>45855</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45510</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>45798</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>44958</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39335,7 +39335,7 @@
         <v>44652</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>45688</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39481,7 +39481,7 @@
         <v>45678</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>45819</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>45953</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>46035</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39778,7 +39778,7 @@
         <v>46036</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39851,7 +39851,7 @@
         <v>46036</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>45805</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39997,7 +39997,7 @@
         <v>46037</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>46037</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40143,7 +40143,7 @@
         <v>45842</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>46041</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>46044</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>44992</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40435,7 +40435,7 @@
         <v>45870</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>45120</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45120</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40654,7 +40654,7 @@
         <v>45364</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>45870</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>45000</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>44848</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
         <v>45472</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>45525</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>45968</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41165,7 +41165,7 @@
         <v>45050</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41238,7 +41238,7 @@
         <v>45050</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>46140</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>46059</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>45294</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>46141</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41608,7 +41608,7 @@
         <v>46136</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41681,7 +41681,7 @@
         <v>45935</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
         <v>46153</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>46153</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>46076</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>46076</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42046,7 +42046,7 @@
         <v>46153</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42119,7 +42119,7 @@
         <v>46153</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42192,7 +42192,7 @@
         <v>46153</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42265,7 +42265,7 @@
         <v>46153</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42338,7 +42338,7 @@
         <v>46154</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42411,7 +42411,7 @@
         <v>46154</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42484,7 +42484,7 @@
         <v>45817</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42557,7 +42557,7 @@
         <v>46113</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>46085</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>46084</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>45337</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>46091</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>46090</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42995,7 +42995,7 @@
         <v>46097</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43068,7 +43068,7 @@
         <v>44825</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         <v>45917</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43214,7 +43214,7 @@
         <v>45845</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>46175</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>46176</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>46183</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>46183</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43589,7 +43589,7 @@
         <v>46182</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>46183</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>46184</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>46184</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43886,7 +43886,7 @@
         <v>46188</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>46198</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>46198</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44105,7 +44105,7 @@
         <v>46198</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44178,7 +44178,7 @@
         <v>46183</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>46203</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44329,7 +44329,7 @@
         <v>46202</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44402,7 +44402,7 @@
         <v>46203</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>46204</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44548,7 +44548,7 @@
         <v>46204</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>46204</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>46204</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44767,7 +44767,7 @@
         <v>46206</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44840,7 +44840,7 @@
         <v>46217</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>46216</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44986,7 +44986,7 @@
         <v>46216</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45059,7 +45059,7 @@
         <v>46267</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>46268</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>46267</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45278,7 +45278,7 @@
         <v>46268</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45351,7 +45351,7 @@
         <v>46224</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45424,7 +45424,7 @@
         <v>46272</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45497,7 +45497,7 @@
         <v>46280</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45575,7 +45575,7 @@
         <v>46268</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>46245</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45721,7 +45721,7 @@
         <v>46287</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45794,7 +45794,7 @@
         <v>45895</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45867,7 +45867,7 @@
         <v>46133</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45940,7 +45940,7 @@
         <v>45792</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46013,7 +46013,7 @@
         <v>46246</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>46246</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>46289</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>45720</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>46083</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46378,7 +46378,7 @@
         <v>45964</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>46289</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46524,7 +46524,7 @@
         <v>46253</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
         <v>46252</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46670,7 +46670,7 @@
         <v>46251</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46743,7 +46743,7 @@
         <v>46251</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46816,7 +46816,7 @@
         <v>46295</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
         <v>45937</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46962,7 +46962,7 @@
         <v>46254</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>46254</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45294</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>45294</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47254,7 +47254,7 @@
         <v>45294</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>46301</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47400,7 +47400,7 @@
         <v>45294</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>45308</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47546,7 +47546,7 @@
         <v>46260</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>46260</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>46303</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47765,7 +47765,7 @@
         <v>46303</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>46260</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47911,7 +47911,7 @@
         <v>46260</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47984,7 +47984,7 @@
         <v>46260</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48057,7 +48057,7 @@
         <v>46260</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48130,7 +48130,7 @@
         <v>46260</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>44624</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48276,7 +48276,7 @@
         <v>44642</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48349,7 +48349,7 @@
         <v>45513</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>44706</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48500,7 +48500,7 @@
         <v>45174</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48573,7 +48573,7 @@
         <v>44785</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45008</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>44900</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>44865</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48865,7 +48865,7 @@
         <v>45257</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48938,7 +48938,7 @@
         <v>45173</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>44900</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49084,7 +49084,7 @@
         <v>45173</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49157,7 +49157,7 @@
         <v>44900</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45534</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49303,7 +49303,7 @@
         <v>45814</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49376,7 +49376,7 @@
         <v>45429</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49449,7 +49449,7 @@
         <v>45831</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>45890</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49595,7 +49595,7 @@
         <v>45979</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>45740</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49741,7 +49741,7 @@
         <v>45740</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49814,7 +49814,7 @@
         <v>45127</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49887,7 +49887,7 @@
         <v>46073</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49960,7 +49960,7 @@
         <v>46083</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>

--- a/Översikt BORÅS.xlsx
+++ b/Översikt BORÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45471</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45671</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45210</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45435</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45187</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>45943</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>45321</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>46042</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44624</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45526</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>44501</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>45204</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45393</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44873</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>44721</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>45316</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45629</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>44546</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45275</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>45351</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>44748</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>45944</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>45982</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45604</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>45393</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>46076</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>44691</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>44817</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>44589</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>45153</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>44949</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>44630</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>45140</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>45153</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45119</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>45846</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>45867</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>44750</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>45093</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>45281</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>45007</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>45379</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>46052</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>44873</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>45348</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>44824</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>45867</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>44544</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>44879</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>45321</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>44958</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>44742</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45267</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>45686</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45629</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>45126</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>45793</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>45793</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>45321</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>45671</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>44750</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>45943</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45826</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>45841</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>45240</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>45264</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>46008</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45260</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>45510</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>45321</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>46198</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>46280</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>46259</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>44873</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>45671</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>46104</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>44512</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>44586</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>44656</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         <v>44631</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>44617</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>44683</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>44544</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>44488</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>44830</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>44817</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44817</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>44538</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>44734</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>44837</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>44586</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>44873</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>44538</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>44510</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>44511</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>44544</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>44887</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>44502</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>44491</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>44523</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>44882</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>44529</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>44673</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>44753</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>44511</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         <v>44873</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>44769</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>44606</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         <v>44642</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>44565</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>44605</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>44845</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>44845</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>44845</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>44624</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>44505</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>44550</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>44678</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>45044</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>45406</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>45264</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>45120</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         <v>45650</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>44897</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>44958</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12647,7 +12647,7 @@
         <v>45646</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>45211</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>45096</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>45119</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>45412</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>45050</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>44896</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>45216</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>45110</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>45194</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>45184</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>45771</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>45666</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>45727</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>45421</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45097</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>44728</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45770</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>45126</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>45194</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>45629</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>45119</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>44916</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>44489</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>45119</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>44866</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>44958</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>45538</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>45232</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>45099</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>45537</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>44546</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>45412</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>45120</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>45120</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45120</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>45379</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>45120</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45062</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45440</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45205</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>45240</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>44844</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>45474</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45329</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45210</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>44980</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>44837</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>45271</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>45772</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>45034</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>45462</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>45887</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>45273</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>45646</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>45062</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>45888</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>45888</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>45888</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>45888</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>45545</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>44577</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>45294</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>44914</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>45268</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>45546</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>45211</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>45321</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>45208</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>44889</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>45762</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45119</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45632</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>44964</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>44900</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>44859</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>45909</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45120</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>44630</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45321</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>45909</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>45776</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>44987</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>45316</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>45575</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>45782</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>44858</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>45637</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45475</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>45587</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>45593</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45784</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>45783</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>44888</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>45783</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>45596</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>45162</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45611</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45721</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45209</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45917</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>45216</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45922</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44639</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>45562</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>44609</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>45670</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45922</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>44552</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45155</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>44515</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45119</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>44964</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>45924</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>44581</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21097,7 +21097,7 @@
         <v>45789</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>45789</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21243,7 +21243,7 @@
         <v>45925</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21316,7 +21316,7 @@
         <v>45726</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>45104</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>45629</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>45142</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>45217</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>45212</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>44910</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>45196</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>44547</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>45929</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>45357</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>45054</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>45931</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22270,7 +22270,7 @@
         <v>45678</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45631</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45671</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>44644</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>44941</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45472</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45579</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45931</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>45931</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>45798</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45579</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>45547</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>45119</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>45432</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>44639</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>45316</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>45593</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>44897</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>45196</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>44564</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         <v>45190</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45582</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>45800</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>45351</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>45803</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>45803</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>45803</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45225</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>45636</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44748</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>44740</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>45274</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45938</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>45812</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>45812</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>44656</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>45015</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>45812</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>45231</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45803</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>45943</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45937</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>45812</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>45205</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45212</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45343</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>45629</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>45817</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>45817</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>45456</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>45148</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         <v>45582</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26101,7 +26101,7 @@
         <v>45735</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26174,7 +26174,7 @@
         <v>44746</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26247,7 +26247,7 @@
         <v>44958</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>45819</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>45472</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>45258</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>45356</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26617,7 +26617,7 @@
         <v>45821</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26690,7 +26690,7 @@
         <v>45099</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>45823</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>45821</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>45947</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>45947</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>45603</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>45126</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>45119</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>45119</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>44959</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>45727</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>45685</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         <v>45723</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>45741</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>45741</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>45827</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>45727</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>45516</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>45058</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>45611</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>45832</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28223,7 +28223,7 @@
         <v>45832</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>45741</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>45953</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>45960</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>45959</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>45951</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>45961</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>45058</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>45119</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>45638</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>45961</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         <v>45836</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>45264</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>44993</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29250,7 +29250,7 @@
         <v>45836</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>45839</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>45120</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>45240</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29542,7 +29542,7 @@
         <v>45119</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45119</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>45103</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29761,7 +29761,7 @@
         <v>45839</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>45841</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>45302</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>44704</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>45392</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45749</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>45629</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>45629</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>45629</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>45239</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30496,7 +30496,7 @@
         <v>45119</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30569,7 +30569,7 @@
         <v>45582</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>45846</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30715,7 +30715,7 @@
         <v>45204</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>45315</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30861,7 +30861,7 @@
         <v>45186</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>45233</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>45758</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31080,7 +31080,7 @@
         <v>45268</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31153,7 +31153,7 @@
         <v>45974</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>45756</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>45120</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>45289</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>44804</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>45477</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>45392</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>45225</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31737,7 +31737,7 @@
         <v>45321</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>44839</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>45866</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>44882</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32034,7 +32034,7 @@
         <v>45612</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32107,7 +32107,7 @@
         <v>45321</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32185,7 +32185,7 @@
         <v>45510</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>45610</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>45316</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>45240</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44916</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>45567</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45176</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>45294</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>44897</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>45321</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>45877</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32993,7 +32993,7 @@
         <v>45982</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>45547</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33144,7 +33144,7 @@
         <v>45982</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45273</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>45113</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>45202</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>45189</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33538,7 +33538,7 @@
         <v>45548</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45982</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33689,7 +33689,7 @@
         <v>46099</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45588</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>46099</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>45197</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>45985</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>45224</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>44854</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34200,7 +34200,7 @@
         <v>45197</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>44949</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>44866</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>44886</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>44886</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>44886</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>45197</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34711,7 +34711,7 @@
         <v>45180</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>46105</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34857,7 +34857,7 @@
         <v>44964</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34930,7 +34930,7 @@
         <v>45215</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>45053</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35076,7 +35076,7 @@
         <v>46104</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>46105</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35222,7 +35222,7 @@
         <v>45168</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>45483</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35368,7 +35368,7 @@
         <v>44875</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>45561</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>45483</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35587,7 +35587,7 @@
         <v>45988</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35660,7 +35660,7 @@
         <v>45462</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35733,7 +35733,7 @@
         <v>46111</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35806,7 +35806,7 @@
         <v>44571</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35879,7 +35879,7 @@
         <v>45992</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35952,7 +35952,7 @@
         <v>45989</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>44914</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36103,7 +36103,7 @@
         <v>45769</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36176,7 +36176,7 @@
         <v>45085</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36249,7 +36249,7 @@
         <v>45538</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36322,7 +36322,7 @@
         <v>44900</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36395,7 +36395,7 @@
         <v>45994</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36468,7 +36468,7 @@
         <v>45994</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>46119</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36614,7 +36614,7 @@
         <v>44489</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45015</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>44995</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>45996</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>46132</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>46128</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>44592</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>45048</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37198,7 +37198,7 @@
         <v>45301</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>44771</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         <v>45546</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37422,7 +37422,7 @@
         <v>45593</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>46008</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>46008</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>45308</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>44656</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37792,7 +37792,7 @@
         <v>45308</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>45350</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>45670</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38016,7 +38016,7 @@
         <v>45855</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>45688</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38162,7 +38162,7 @@
         <v>45615</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38235,7 +38235,7 @@
         <v>45701</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>45713</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38381,7 +38381,7 @@
         <v>45715</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>45688</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>45699</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38600,7 +38600,7 @@
         <v>45453</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>44538</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45176</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38824,7 +38824,7 @@
         <v>45098</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>46147</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45863</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>45855</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45510</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>45798</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>44958</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39335,7 +39335,7 @@
         <v>44652</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>45688</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39481,7 +39481,7 @@
         <v>45678</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>45819</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>45953</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>46035</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39778,7 +39778,7 @@
         <v>46036</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39851,7 +39851,7 @@
         <v>46036</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>45805</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39997,7 +39997,7 @@
         <v>46037</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40070,7 +40070,7 @@
         <v>46037</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40143,7 +40143,7 @@
         <v>45842</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>46041</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>46044</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>44992</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40435,7 +40435,7 @@
         <v>45870</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>45120</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>45120</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40654,7 +40654,7 @@
         <v>45364</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>45870</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>45000</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>44848</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
         <v>45472</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>45525</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>45968</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41165,7 +41165,7 @@
         <v>45050</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41238,7 +41238,7 @@
         <v>45050</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>46140</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>46059</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>45294</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>46141</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41608,7 +41608,7 @@
         <v>46136</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41681,7 +41681,7 @@
         <v>45935</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
         <v>46153</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>46153</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>46076</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>46076</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42046,7 +42046,7 @@
         <v>46153</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42119,7 +42119,7 @@
         <v>46153</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42192,7 +42192,7 @@
         <v>46153</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42265,7 +42265,7 @@
         <v>46153</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42338,7 +42338,7 @@
         <v>46154</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42411,7 +42411,7 @@
         <v>46154</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42484,7 +42484,7 @@
         <v>45817</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42557,7 +42557,7 @@
         <v>46113</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>46085</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>46084</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>45337</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>46091</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>46090</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42995,7 +42995,7 @@
         <v>46097</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43068,7 +43068,7 @@
         <v>44825</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         <v>45917</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43214,7 +43214,7 @@
         <v>45845</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>46175</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>46176</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43433,7 +43433,7 @@
         <v>46183</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>46183</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43589,7 +43589,7 @@
         <v>46182</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>46183</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>46184</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>46184</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43886,7 +43886,7 @@
         <v>46188</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>46198</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
         <v>46198</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44105,7 +44105,7 @@
         <v>46198</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44178,7 +44178,7 @@
         <v>46183</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>46203</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44329,7 +44329,7 @@
         <v>46202</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44402,7 +44402,7 @@
         <v>46203</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>46204</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44548,7 +44548,7 @@
         <v>46204</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>46204</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>46204</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44767,7 +44767,7 @@
         <v>46206</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44840,7 +44840,7 @@
         <v>46217</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>46216</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44986,7 +44986,7 @@
         <v>46216</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45059,7 +45059,7 @@
         <v>46267</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>46268</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>46267</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45278,7 +45278,7 @@
         <v>46268</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45351,7 +45351,7 @@
         <v>46224</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45424,7 +45424,7 @@
         <v>46272</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45497,7 +45497,7 @@
         <v>46280</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45575,7 +45575,7 @@
         <v>46268</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>46245</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45721,7 +45721,7 @@
         <v>46287</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45794,7 +45794,7 @@
         <v>45895</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45867,7 +45867,7 @@
         <v>46133</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45940,7 +45940,7 @@
         <v>45792</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46013,7 +46013,7 @@
         <v>46246</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>46246</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>46289</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>45720</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>46083</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46378,7 +46378,7 @@
         <v>45964</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46451,7 +46451,7 @@
         <v>46289</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46524,7 +46524,7 @@
         <v>46253</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
         <v>46252</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46670,7 +46670,7 @@
         <v>46251</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46743,7 +46743,7 @@
         <v>46251</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46816,7 +46816,7 @@
         <v>46295</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
         <v>45937</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46962,7 +46962,7 @@
         <v>46254</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>46254</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45294</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>45294</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47254,7 +47254,7 @@
         <v>45294</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>46301</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47400,7 +47400,7 @@
         <v>45294</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>45308</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47546,7 +47546,7 @@
         <v>46260</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>46260</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>46303</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47765,7 +47765,7 @@
         <v>46303</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>46260</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47911,7 +47911,7 @@
         <v>46260</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47984,7 +47984,7 @@
         <v>46260</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48057,7 +48057,7 @@
         <v>46260</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48130,7 +48130,7 @@
         <v>46260</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>44624</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48276,7 +48276,7 @@
         <v>44642</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48349,7 +48349,7 @@
         <v>45513</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>44706</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48500,7 +48500,7 @@
         <v>45174</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48573,7 +48573,7 @@
         <v>44785</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>45008</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>44900</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>44865</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48865,7 +48865,7 @@
         <v>45257</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48938,7 +48938,7 @@
         <v>45173</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>44900</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49084,7 +49084,7 @@
         <v>45173</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49157,7 +49157,7 @@
         <v>44900</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45534</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49303,7 +49303,7 @@
         <v>45814</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49376,7 +49376,7 @@
         <v>45429</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49449,7 +49449,7 @@
         <v>45831</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>45890</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49595,7 +49595,7 @@
         <v>45979</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>45740</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49741,7 +49741,7 @@
         <v>45740</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49814,7 +49814,7 @@
         <v>45127</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49887,7 +49887,7 @@
         <v>46073</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49960,7 +49960,7 @@
         <v>46083</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>

--- a/Översikt BORÅS.xlsx
+++ b/Översikt BORÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45471</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45671</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45210</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45435</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45943</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45187</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>45321</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>46042</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44624</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45204</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>45526</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44501</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45393</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44873</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>44721</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>45351</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45316</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>45944</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>45604</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44748</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>45393</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>46076</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45275</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>45629</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>46308</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>44691</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>44817</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>44750</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>45119</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>45153</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>44630</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>45140</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45093</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>45281</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>45379</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>45007</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>44949</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>44589</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>45153</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>46052</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>45846</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>45867</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>44873</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45348</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>44824</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>45867</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>44544</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>44958</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>45510</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>45671</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45267</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>45321</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>45240</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>45264</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>45943</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44742</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>46008</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>44750</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>46198</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>45321</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>44879</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>45126</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>45321</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>46280</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>45260</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>45686</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>45629</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>46259</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>45793</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>45793</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>45826</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>45841</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>44873</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>45671</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>46104</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>44586</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>44512</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44656</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44631</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>44617</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>44683</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>44544</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>44488</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>44830</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>44817</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>44817</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>44538</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>44734</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>44837</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>44586</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>44873</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>44538</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>44510</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>44511</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>44544</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>44887</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>44502</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>44491</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>44523</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>44511</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>44606</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>44605</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>44845</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>44845</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>44845</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>44624</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>44769</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>44673</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>44753</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>44873</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>44565</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>44550</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>44882</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>44529</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>44642</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44505</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>44678</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>45678</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>45268</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>44489</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>44489</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>45575</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>44515</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>44609</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>45119</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>44740</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>45561</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44958</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44897</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>44552</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>45294</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>45110</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>44900</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>45050</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>45050</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>45034</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>45054</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>45351</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>44728</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>45232</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>45119</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>45588</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>45510</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>45212</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>45197</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>45000</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>44639</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>45650</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>45629</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>45240</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>45240</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>45462</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>45099</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>45749</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>45015</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>45727</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>45666</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>44910</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>44889</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>44916</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>45638</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>45356</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>45462</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>45231</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>44804</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>45294</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>45406</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>45225</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>45271</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>45538</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>45208</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>44980</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>45321</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>45180</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>44897</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>45190</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>45126</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
         <v>44581</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>45119</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>45758</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         <v>45233</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>45316</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>44858</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>45120</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>45120</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>45120</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>45562</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>45258</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>45194</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>45412</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17611,7 +17611,7 @@
         <v>45537</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>44888</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>45525</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>45120</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>45120</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>44958</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>44993</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>45350</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>45629</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45097</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>45379</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>45058</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>45264</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>45155</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>45870</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>45453</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45855</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>45646</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>46147</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>44844</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>45688</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45819</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45210</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45887</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         <v>45611</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45888</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>45888</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>45888</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45888</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19733,7 +19733,7 @@
         <v>45805</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>45184</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>45510</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>44547</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20025,7 +20025,7 @@
         <v>45104</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>45211</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44630</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>45842</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>45968</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>45855</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>45098</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20536,7 +20536,7 @@
         <v>45197</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>44644</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>45953</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         <v>46141</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>45294</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>46140</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45196</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>44656</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>45316</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>45316</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>45593</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>45202</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>45096</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>45456</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45870</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>45909</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>44914</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>45176</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>45909</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>44987</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>44571</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45215</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>45547</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45343</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45547</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>45917</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45922</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45922</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>46136</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>45924</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>45925</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>44964</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45646</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>45935</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>45929</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>45205</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>45931</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>45931</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>46153</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>46153</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>45931</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>46153</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>46153</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>45196</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>46153</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>45301</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>45938</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45803</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>46153</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>45308</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>45943</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>45937</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>46113</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>45685</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>45947</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>45947</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>46154</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>46154</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>45953</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>45959</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>45951</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>45961</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>45053</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>44859</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45960</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>45961</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>44848</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>45273</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>45337</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>44592</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45315</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44896</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>45974</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>44825</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>45085</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>45472</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>45412</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>45357</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26280,7 +26280,7 @@
         <v>44964</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>45982</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26431,7 +26431,7 @@
         <v>45982</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26509,7 +26509,7 @@
         <v>45985</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>45982</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>45546</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>45103</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26830,7 +26830,7 @@
         <v>45989</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>45224</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>45988</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>45762</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>45992</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27205,7 +27205,7 @@
         <v>45264</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>45629</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>45629</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>45629</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>45994</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45119</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>45994</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>45996</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45176</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>45603</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>45308</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>44958</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>45770</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>45678</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>46008</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44941</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>46008</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28456,7 +28456,7 @@
         <v>45268</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>45329</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>45637</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>45715</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>45688</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>45688</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>45917</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>45713</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>45701</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29113,7 +29113,7 @@
         <v>45845</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>45699</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29259,7 +29259,7 @@
         <v>45615</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29332,7 +29332,7 @@
         <v>44900</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>45629</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29478,7 +29478,7 @@
         <v>46035</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29551,7 +29551,7 @@
         <v>45321</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>45321</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>46176</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>46175</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>46037</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>46036</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29999,7 +29999,7 @@
         <v>46036</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>46037</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>46041</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>45120</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45217</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44704</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>46044</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44897</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>44652</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>45546</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>46182</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>45204</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>45772</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>46183</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31026,7 +31026,7 @@
         <v>46059</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>46183</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31182,7 +31182,7 @@
         <v>45050</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>46183</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>46184</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>44839</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31479,7 +31479,7 @@
         <v>46184</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>45120</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>44959</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>45162</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>44964</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>46188</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>44639</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>46076</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>45212</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>45239</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>45538</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>46076</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>46084</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>45817</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>44958</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32574,7 +32574,7 @@
         <v>46085</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32647,7 +32647,7 @@
         <v>45148</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32720,7 +32720,7 @@
         <v>45015</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>44546</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32866,7 +32866,7 @@
         <v>45205</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>46090</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33012,7 +33012,7 @@
         <v>46091</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         <v>45044</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>45582</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33231,7 +33231,7 @@
         <v>46097</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>46099</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33377,7 +33377,7 @@
         <v>44866</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33450,7 +33450,7 @@
         <v>44886</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33523,7 +33523,7 @@
         <v>46099</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>44949</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>44886</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>44886</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>44854</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>45189</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33961,7 +33961,7 @@
         <v>46104</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34034,7 +34034,7 @@
         <v>45771</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34107,7 +34107,7 @@
         <v>45593</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34180,7 +34180,7 @@
         <v>46105</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>46105</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>45548</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34399,7 +34399,7 @@
         <v>46198</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34472,7 +34472,7 @@
         <v>46198</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>46198</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>45483</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>45483</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>46111</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34837,7 +34837,7 @@
         <v>45756</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34910,7 +34910,7 @@
         <v>45440</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34983,7 +34983,7 @@
         <v>46119</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>46202</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>45670</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45058</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>46128</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>45474</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>44866</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>46183</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>45240</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>46204</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35718,7 +35718,7 @@
         <v>46132</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>46204</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35864,7 +35864,7 @@
         <v>46204</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>46203</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>45113</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>46204</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36156,7 +36156,7 @@
         <v>46203</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>45197</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>45186</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36375,7 +36375,7 @@
         <v>44538</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>45211</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36526,7 +36526,7 @@
         <v>45798</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>45863</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>45477</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36745,7 +36745,7 @@
         <v>46206</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36818,7 +36818,7 @@
         <v>45119</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         <v>44771</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
         <v>45225</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37042,7 +37042,7 @@
         <v>44875</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>45126</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>45631</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37261,7 +37261,7 @@
         <v>46216</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
         <v>45321</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37412,7 +37412,7 @@
         <v>46216</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37485,7 +37485,7 @@
         <v>45120</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         <v>46217</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37631,7 +37631,7 @@
         <v>44995</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37704,7 +37704,7 @@
         <v>46224</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37777,7 +37777,7 @@
         <v>45289</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
         <v>45545</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37923,7 +37923,7 @@
         <v>45769</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>45579</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38069,7 +38069,7 @@
         <v>45099</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38147,7 +38147,7 @@
         <v>45579</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>44564</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>45062</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38366,7 +38366,7 @@
         <v>45062</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38439,7 +38439,7 @@
         <v>45611</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38512,7 +38512,7 @@
         <v>46280</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>46272</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38663,7 +38663,7 @@
         <v>45670</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38736,7 +38736,7 @@
         <v>45364</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38809,7 +38809,7 @@
         <v>45792</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38882,7 +38882,7 @@
         <v>45895</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38955,7 +38955,7 @@
         <v>45671</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39028,7 +39028,7 @@
         <v>44577</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39101,7 +39101,7 @@
         <v>46133</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
         <v>45472</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39247,7 +39247,7 @@
         <v>46287</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>45636</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>45119</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>45119</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>45119</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>44916</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39685,7 +39685,7 @@
         <v>45120</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39758,7 +39758,7 @@
         <v>45120</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39831,7 +39831,7 @@
         <v>45632</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>44837</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>45048</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40050,7 +40050,7 @@
         <v>46289</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>46245</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>46246</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>46246</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>44746</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40415,7 +40415,7 @@
         <v>45119</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40488,7 +40488,7 @@
         <v>46289</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>45516</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>45216</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>44992</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45273</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40853,7 +40853,7 @@
         <v>45964</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40926,7 +40926,7 @@
         <v>45119</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40999,7 +40999,7 @@
         <v>45421</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41072,7 +41072,7 @@
         <v>45720</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41145,7 +41145,7 @@
         <v>46083</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41218,7 +41218,7 @@
         <v>45194</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41291,7 +41291,7 @@
         <v>45119</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>44748</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>45302</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41520,7 +41520,7 @@
         <v>45432</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>45216</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41666,7 +41666,7 @@
         <v>45321</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>44914</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41817,7 +41817,7 @@
         <v>46251</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41890,7 +41890,7 @@
         <v>45168</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41963,7 +41963,7 @@
         <v>46252</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42036,7 +42036,7 @@
         <v>45119</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>46295</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>46251</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42255,7 +42255,7 @@
         <v>45741</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42328,7 +42328,7 @@
         <v>45593</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42401,7 +42401,7 @@
         <v>46254</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>46254</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>46253</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>45294</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>45937</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>45582</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42839,7 +42839,7 @@
         <v>45776</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45783</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42985,7 +42985,7 @@
         <v>45782</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43058,7 +43058,7 @@
         <v>45783</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43131,7 +43131,7 @@
         <v>45475</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43204,7 +43204,7 @@
         <v>45294</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43277,7 +43277,7 @@
         <v>45294</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>46301</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43423,7 +43423,7 @@
         <v>45587</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43496,7 +43496,7 @@
         <v>45308</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43569,7 +43569,7 @@
         <v>45209</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43642,7 +43642,7 @@
         <v>45721</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43715,7 +43715,7 @@
         <v>45784</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43788,7 +43788,7 @@
         <v>45294</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43861,7 +43861,7 @@
         <v>45596</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>46303</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44007,7 +44007,7 @@
         <v>46303</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44080,7 +44080,7 @@
         <v>46260</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44153,7 +44153,7 @@
         <v>46260</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44226,7 +44226,7 @@
         <v>46260</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45789</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>45789</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>46260</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>46260</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44591,7 +44591,7 @@
         <v>46260</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44664,7 +44664,7 @@
         <v>45142</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44737,7 +44737,7 @@
         <v>45726</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>46260</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>46306</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>46306</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>46306</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>46306</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>46306</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45248,7 +45248,7 @@
         <v>45798</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45803</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45399,7 +45399,7 @@
         <v>46308</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45800</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>45803</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45623,7 +45623,7 @@
         <v>45803</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45696,7 +45696,7 @@
         <v>46310</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45769,7 +45769,7 @@
         <v>45274</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45842,7 +45842,7 @@
         <v>45812</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45915,7 +45915,7 @@
         <v>44656</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>45812</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45812</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         <v>45812</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46207,7 +46207,7 @@
         <v>45582</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46280,7 +46280,7 @@
         <v>46268</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46353,7 +46353,7 @@
         <v>45817</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46426,7 +46426,7 @@
         <v>46268</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>45817</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46572,7 +46572,7 @@
         <v>45735</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46645,7 +46645,7 @@
         <v>45819</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45821</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46791,7 +46791,7 @@
         <v>46267</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>45821</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45472</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47010,7 +47010,7 @@
         <v>46268</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47083,7 +47083,7 @@
         <v>45823</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47156,7 +47156,7 @@
         <v>46267</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47229,7 +47229,7 @@
         <v>45727</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47302,7 +47302,7 @@
         <v>45727</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47375,7 +47375,7 @@
         <v>45741</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>46310</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>45741</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45723</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47667,7 +47667,7 @@
         <v>45827</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47740,7 +47740,7 @@
         <v>45832</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>45832</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47886,7 +47886,7 @@
         <v>45839</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>45839</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48032,7 +48032,7 @@
         <v>45836</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48105,7 +48105,7 @@
         <v>45836</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48178,7 +48178,7 @@
         <v>45841</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45392</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48324,7 +48324,7 @@
         <v>45846</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48397,7 +48397,7 @@
         <v>45392</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48470,7 +48470,7 @@
         <v>45866</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>44882</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48616,7 +48616,7 @@
         <v>45610</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>45567</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48762,7 +48762,7 @@
         <v>45612</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>45877</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48908,7 +48908,7 @@
         <v>45174</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48981,7 +48981,7 @@
         <v>44785</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49054,7 +49054,7 @@
         <v>45008</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49127,7 +49127,7 @@
         <v>44624</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49200,7 +49200,7 @@
         <v>44900</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49273,7 +49273,7 @@
         <v>44865</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45257</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49419,7 +49419,7 @@
         <v>45173</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49492,7 +49492,7 @@
         <v>44642</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49565,7 +49565,7 @@
         <v>44900</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>45513</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49711,7 +49711,7 @@
         <v>44706</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49789,7 +49789,7 @@
         <v>45173</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49862,7 +49862,7 @@
         <v>44900</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49935,7 +49935,7 @@
         <v>45534</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>45814</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50081,7 +50081,7 @@
         <v>45429</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>45831</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         <v>45890</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50300,7 +50300,7 @@
         <v>45979</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50373,7 +50373,7 @@
         <v>45740</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50446,7 +50446,7 @@
         <v>45740</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50519,7 +50519,7 @@
         <v>45127</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>46073</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50665,7 +50665,7 @@
         <v>46083</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>

--- a/Översikt BORÅS.xlsx
+++ b/Översikt BORÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45471</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45671</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>45210</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45435</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45943</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45187</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>45321</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>46042</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44624</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45204</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>45526</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44501</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45393</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44873</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>44721</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>45351</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45316</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>45944</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>45604</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>44748</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>45393</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>46076</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45275</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>45629</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>46308</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>44691</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>44817</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>44750</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>45119</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>45153</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>44630</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>45140</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>45093</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>45281</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>45379</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>45007</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>44949</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>44589</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>45153</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>46052</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>45846</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>45867</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>44873</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45348</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>44824</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>45867</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>44544</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>44958</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>45510</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>45671</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45267</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>45321</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>45240</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         <v>45264</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>45943</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44742</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>46008</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>44750</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>46198</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>45321</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>44879</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>45126</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>45321</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>46280</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>45260</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>45686</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>45629</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>46259</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>45793</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>45793</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>45826</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>45841</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>44873</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>45671</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>46104</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>44586</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>44512</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44656</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44631</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>44617</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>44683</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>44544</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>44488</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>44830</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>44817</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>44817</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>44538</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>44734</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>44837</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>44586</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>44873</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>44538</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>44510</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>44511</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>44544</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>44887</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>44502</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>44491</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>44523</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>44511</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>44606</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>44605</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>44845</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>44845</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>44845</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>44624</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>44769</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>44673</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>44753</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>44873</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>44565</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>44550</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>44882</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>44529</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>44642</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44505</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>44678</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>45678</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>45268</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>44489</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>44489</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>45575</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>44515</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>44609</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>45119</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>44740</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>45561</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44958</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44897</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>44552</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>45294</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>45110</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>44900</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>45050</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>45050</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>45034</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>45054</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>45351</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>44728</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>45232</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>45119</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>45588</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>45510</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>45212</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>45197</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>45000</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>44639</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>45650</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>45629</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>45240</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>45240</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>45462</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>45099</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>45749</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>45015</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>45727</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>45666</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>44910</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>44889</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>44916</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>45638</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>45356</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>45462</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>45231</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>44804</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>45294</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>45406</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>45225</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>45271</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>45538</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>45208</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>44980</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>45321</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>45180</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>44897</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>45190</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>45126</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
         <v>44581</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>45119</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>45758</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         <v>45233</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>45316</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>44858</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>45120</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>45120</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>45120</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>45562</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>45258</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>45194</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>45412</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17611,7 +17611,7 @@
         <v>45537</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>44888</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>45525</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>45120</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>45120</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>44958</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>44993</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>45350</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>45629</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45097</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>45379</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>45058</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>45264</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>45155</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>45870</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>45453</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45855</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>45646</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>46147</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>44844</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>45688</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45819</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45210</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45887</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         <v>45611</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45888</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>45888</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>45888</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45888</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19733,7 +19733,7 @@
         <v>45805</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>45184</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>45510</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>44547</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20025,7 +20025,7 @@
         <v>45104</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>45211</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44630</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>45842</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>45968</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>45855</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>45098</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20536,7 +20536,7 @@
         <v>45197</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>44644</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>45953</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         <v>46141</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>45294</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>46140</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45196</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>44656</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>45316</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>45316</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>45593</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>45202</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>45096</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>45456</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45870</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>45909</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>44914</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>45176</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>45909</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>44987</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>44571</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45215</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>45547</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45343</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45547</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>45917</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45922</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45922</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>46136</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>45924</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>45925</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>44964</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45646</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>45935</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>45929</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>45205</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>45931</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>45931</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>46153</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>46153</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>45931</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>46153</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>46153</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>45196</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>46153</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>45301</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>45938</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45803</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>46153</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>45308</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>45943</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>45937</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>46113</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>45685</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>45947</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>45947</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>46154</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>46154</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>45953</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>45959</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>45951</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>45961</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>45053</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>44859</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45960</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>45961</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25404,7 +25404,7 @@
         <v>44848</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25477,7 +25477,7 @@
         <v>45273</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>45337</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>44592</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45315</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44896</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>45974</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>44825</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>45085</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         <v>45472</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>45412</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>45357</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26280,7 +26280,7 @@
         <v>44964</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>45982</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26431,7 +26431,7 @@
         <v>45982</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26509,7 +26509,7 @@
         <v>45985</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>45982</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>45546</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>45103</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26830,7 +26830,7 @@
         <v>45989</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>45224</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>45988</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>45762</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>45992</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27205,7 +27205,7 @@
         <v>45264</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>45629</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>45629</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>45629</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>45994</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45119</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>45994</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>45996</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45176</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>45603</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>45308</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>44958</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>45770</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>45678</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>46008</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44941</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>46008</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28456,7 +28456,7 @@
         <v>45268</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>45329</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>45637</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>45715</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>45688</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>45688</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>45917</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>45713</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>45701</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29113,7 +29113,7 @@
         <v>45845</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>45699</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29259,7 +29259,7 @@
         <v>45615</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29332,7 +29332,7 @@
         <v>44900</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>45629</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29478,7 +29478,7 @@
         <v>46035</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29551,7 +29551,7 @@
         <v>45321</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>45321</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>46176</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>46175</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>46037</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>46036</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29999,7 +29999,7 @@
         <v>46036</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>46037</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>46041</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>45120</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45217</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44704</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>46044</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44897</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>44652</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>45546</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>46182</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>45204</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>45772</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>46183</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31026,7 +31026,7 @@
         <v>46059</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>46183</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31182,7 +31182,7 @@
         <v>45050</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>46183</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>46184</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>44839</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31479,7 +31479,7 @@
         <v>46184</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>45120</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>44959</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>45162</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>44964</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>46188</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>44639</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>46076</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>45212</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>45239</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>45538</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>46076</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>46084</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>45817</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>44958</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32574,7 +32574,7 @@
         <v>46085</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32647,7 +32647,7 @@
         <v>45148</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32720,7 +32720,7 @@
         <v>45015</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>44546</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32866,7 +32866,7 @@
         <v>45205</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>46090</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33012,7 +33012,7 @@
         <v>46091</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         <v>45044</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>45582</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33231,7 +33231,7 @@
         <v>46097</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>46099</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33377,7 +33377,7 @@
         <v>44866</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33450,7 +33450,7 @@
         <v>44886</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33523,7 +33523,7 @@
         <v>46099</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>44949</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>44886</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>44886</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>44854</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>45189</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33961,7 +33961,7 @@
         <v>46104</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34034,7 +34034,7 @@
         <v>45771</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34107,7 +34107,7 @@
         <v>45593</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34180,7 +34180,7 @@
         <v>46105</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>46105</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>45548</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34399,7 +34399,7 @@
         <v>46198</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34472,7 +34472,7 @@
         <v>46198</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>46198</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>45483</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>45483</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>46111</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34837,7 +34837,7 @@
         <v>45756</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34910,7 +34910,7 @@
         <v>45440</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34983,7 +34983,7 @@
         <v>46119</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>46202</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>45670</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45058</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>46128</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>45474</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>44866</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>46183</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>45240</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>46204</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35718,7 +35718,7 @@
         <v>46132</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>46204</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35864,7 +35864,7 @@
         <v>46204</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>46203</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>45113</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>46204</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36156,7 +36156,7 @@
         <v>46203</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>45197</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>45186</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36375,7 +36375,7 @@
         <v>44538</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>45211</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36526,7 +36526,7 @@
         <v>45798</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>45863</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>45477</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36745,7 +36745,7 @@
         <v>46206</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36818,7 +36818,7 @@
         <v>45119</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         <v>44771</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
         <v>45225</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37042,7 +37042,7 @@
         <v>44875</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>45126</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>45631</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37261,7 +37261,7 @@
         <v>46216</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
         <v>45321</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37412,7 +37412,7 @@
         <v>46216</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37485,7 +37485,7 @@
         <v>45120</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         <v>46217</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37631,7 +37631,7 @@
         <v>44995</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37704,7 +37704,7 @@
         <v>46224</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37777,7 +37777,7 @@
         <v>45289</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
         <v>45545</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37923,7 +37923,7 @@
         <v>45769</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>45579</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38069,7 +38069,7 @@
         <v>45099</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38147,7 +38147,7 @@
         <v>45579</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>44564</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>45062</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38366,7 +38366,7 @@
         <v>45062</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38439,7 +38439,7 @@
         <v>45611</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38512,7 +38512,7 @@
         <v>46280</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>46272</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38663,7 +38663,7 @@
         <v>45670</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38736,7 +38736,7 @@
         <v>45364</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38809,7 +38809,7 @@
         <v>45792</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38882,7 +38882,7 @@
         <v>45895</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38955,7 +38955,7 @@
         <v>45671</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39028,7 +39028,7 @@
         <v>44577</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39101,7 +39101,7 @@
         <v>46133</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
         <v>45472</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39247,7 +39247,7 @@
         <v>46287</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>45636</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>45119</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>45119</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>45119</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>44916</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39685,7 +39685,7 @@
         <v>45120</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39758,7 +39758,7 @@
         <v>45120</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39831,7 +39831,7 @@
         <v>45632</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>44837</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>45048</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40050,7 +40050,7 @@
         <v>46289</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>46245</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>46246</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>46246</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>44746</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40415,7 +40415,7 @@
         <v>45119</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40488,7 +40488,7 @@
         <v>46289</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>45516</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>45216</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>44992</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45273</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40853,7 +40853,7 @@
         <v>45964</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40926,7 +40926,7 @@
         <v>45119</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40999,7 +40999,7 @@
         <v>45421</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41072,7 +41072,7 @@
         <v>45720</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41145,7 +41145,7 @@
         <v>46083</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41218,7 +41218,7 @@
         <v>45194</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41291,7 +41291,7 @@
         <v>45119</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>44748</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>45302</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41520,7 +41520,7 @@
         <v>45432</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>45216</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41666,7 +41666,7 @@
         <v>45321</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>44914</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41817,7 +41817,7 @@
         <v>46251</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41890,7 +41890,7 @@
         <v>45168</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41963,7 +41963,7 @@
         <v>46252</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42036,7 +42036,7 @@
         <v>45119</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>46295</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>46251</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42255,7 +42255,7 @@
         <v>45741</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42328,7 +42328,7 @@
         <v>45593</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42401,7 +42401,7 @@
         <v>46254</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>46254</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>46253</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>45294</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>45937</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>45582</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42839,7 +42839,7 @@
         <v>45776</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45783</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42985,7 +42985,7 @@
         <v>45782</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43058,7 +43058,7 @@
         <v>45783</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43131,7 +43131,7 @@
         <v>45475</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43204,7 +43204,7 @@
         <v>45294</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43277,7 +43277,7 @@
         <v>45294</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>46301</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43423,7 +43423,7 @@
         <v>45587</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43496,7 +43496,7 @@
         <v>45308</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43569,7 +43569,7 @@
         <v>45209</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43642,7 +43642,7 @@
         <v>45721</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43715,7 +43715,7 @@
         <v>45784</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43788,7 +43788,7 @@
         <v>45294</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43861,7 +43861,7 @@
         <v>45596</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>46303</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44007,7 +44007,7 @@
         <v>46303</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44080,7 +44080,7 @@
         <v>46260</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44153,7 +44153,7 @@
         <v>46260</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44226,7 +44226,7 @@
         <v>46260</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45789</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>45789</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>46260</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>46260</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44591,7 +44591,7 @@
         <v>46260</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44664,7 +44664,7 @@
         <v>45142</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44737,7 +44737,7 @@
         <v>45726</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>46260</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>46306</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>46306</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>46306</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>46306</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>46306</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45248,7 +45248,7 @@
         <v>45798</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45803</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45399,7 +45399,7 @@
         <v>46308</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45800</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>45803</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45623,7 +45623,7 @@
         <v>45803</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45696,7 +45696,7 @@
         <v>46310</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45769,7 +45769,7 @@
         <v>45274</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45842,7 +45842,7 @@
         <v>45812</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45915,7 +45915,7 @@
         <v>44656</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>45812</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45812</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         <v>45812</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46207,7 +46207,7 @@
         <v>45582</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46280,7 +46280,7 @@
         <v>46268</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46353,7 +46353,7 @@
         <v>45817</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46426,7 +46426,7 @@
         <v>46268</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>45817</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46572,7 +46572,7 @@
         <v>45735</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46645,7 +46645,7 @@
         <v>45819</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45821</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46791,7 +46791,7 @@
         <v>46267</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>45821</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45472</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47010,7 +47010,7 @@
         <v>46268</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47083,7 +47083,7 @@
         <v>45823</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47156,7 +47156,7 @@
         <v>46267</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47229,7 +47229,7 @@
         <v>45727</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47302,7 +47302,7 @@
         <v>45727</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47375,7 +47375,7 @@
         <v>45741</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>46310</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>45741</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45723</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47667,7 +47667,7 @@
         <v>45827</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47740,7 +47740,7 @@
         <v>45832</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>45832</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47886,7 +47886,7 @@
         <v>45839</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>45839</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48032,7 +48032,7 @@
         <v>45836</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48105,7 +48105,7 @@
         <v>45836</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48178,7 +48178,7 @@
         <v>45841</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45392</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48324,7 +48324,7 @@
         <v>45846</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48397,7 +48397,7 @@
         <v>45392</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48470,7 +48470,7 @@
         <v>45866</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>44882</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48616,7 +48616,7 @@
         <v>45610</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>45567</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48762,7 +48762,7 @@
         <v>45612</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>45877</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48908,7 +48908,7 @@
         <v>45174</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48981,7 +48981,7 @@
         <v>44785</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49054,7 +49054,7 @@
         <v>45008</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49127,7 +49127,7 @@
         <v>44624</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49200,7 +49200,7 @@
         <v>44900</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49273,7 +49273,7 @@
         <v>44865</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45257</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49419,7 +49419,7 @@
         <v>45173</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49492,7 +49492,7 @@
         <v>44642</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49565,7 +49565,7 @@
         <v>44900</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49638,7 +49638,7 @@
         <v>45513</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49711,7 +49711,7 @@
         <v>44706</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49789,7 +49789,7 @@
         <v>45173</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49862,7 +49862,7 @@
         <v>44900</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49935,7 +49935,7 @@
         <v>45534</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>45814</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50081,7 +50081,7 @@
         <v>45429</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>45831</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         <v>45890</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50300,7 +50300,7 @@
         <v>45979</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50373,7 +50373,7 @@
         <v>45740</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50446,7 +50446,7 @@
         <v>45740</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50519,7 +50519,7 @@
         <v>45127</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>46073</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50665,7 +50665,7 @@
         <v>46083</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>

--- a/Översikt BORÅS.xlsx
+++ b/Översikt BORÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45471</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45210</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45671</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45435</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45943</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45187</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>46042</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45321</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44624</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45204</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>45393</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>44501</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>45526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44873</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>44721</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>45944</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>45316</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>45982</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>45393</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>45629</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>45604</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>46076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>46308</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>44748</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>45275</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45351</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>44691</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>44817</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>45140</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>44949</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>45379</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>46052</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>45846</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>45867</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>44630</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>45119</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>45093</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>44589</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>45153</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>45153</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44750</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>45281</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>45007</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>44873</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45348</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>44824</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>45867</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>44544</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>45267</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>44879</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>45260</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>45510</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>45943</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>44958</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>44742</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>46198</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>45686</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>45629</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>46008</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>46280</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>45793</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>45793</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>45826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>45841</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>46259</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>45321</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>44750</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>45321</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>45126</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>45321</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>45671</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>45240</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>45264</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>44873</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>45671</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>46104</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>44586</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>44512</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44656</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44631</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>44617</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>44683</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>44544</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>44830</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>44538</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>44817</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>44817</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>44734</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>44837</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>44586</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>44873</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>44538</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>44510</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>44511</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>44544</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>44887</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>44502</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>44523</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>44511</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>44606</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>44605</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>44845</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>44845</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>44624</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
         <v>44845</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>44769</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44673</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>44753</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>44873</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>44565</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>44550</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>44882</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>44529</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>44642</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>44505</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>44678</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>45048</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>45887</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>45646</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>45888</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>45888</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         <v>45301</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>44771</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>45546</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>45888</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>45412</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>45050</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>45888</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>45593</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>45194</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45308</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44656</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>45308</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>45350</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>44844</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>45670</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>45210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>45406</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>45909</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>45909</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44987</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44825</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>45510</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>44958</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>44652</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>45678</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45917</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>45922</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45922</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45924</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>45925</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>44992</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45917</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>45929</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>45931</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45120</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45120</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45845</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45364</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>45931</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>45000</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45931</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>44848</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>45472</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>45525</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>45050</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>45050</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>45938</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>46175</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45264</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45803</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45943</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>45120</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>46176</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>45650</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45937</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>44958</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>44916</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44958</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45538</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45119</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>45947</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>45947</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>46183</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>46183</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45184</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45666</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>46182</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>45421</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>46183</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>44728</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45953</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45960</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45959</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>45126</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45951</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>45194</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         <v>46184</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>45629</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>46184</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>45119</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>45961</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>46188</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>45961</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>45119</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>44866</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>45232</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>45537</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>45412</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>46198</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>46198</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>45440</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>45205</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>45974</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45240</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>44980</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>46198</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>45379</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>46183</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>46203</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>45034</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>46202</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>45982</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>45982</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>46203</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>45982</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>46204</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>46204</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45062</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>46204</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>44914</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>45268</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>45985</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>45211</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>45321</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
         <v>45208</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20995,7 +20995,7 @@
         <v>46204</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>46206</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>45762</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45988</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>45992</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45119</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45632</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>45989</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>45994</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45994</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>45474</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>45996</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>46217</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>46216</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>46216</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>45776</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45782</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>46224</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22319,7 +22319,7 @@
         <v>45475</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>45587</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>45784</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>45783</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>46008</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45783</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>46008</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>44837</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45596</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>45721</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>45209</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45688</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45615</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>45701</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>45713</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45715</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>45688</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>45699</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>46280</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>45789</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>45789</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>45726</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>45142</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>46035</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>46036</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>46036</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>46037</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>46037</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24368,7 +24368,7 @@
         <v>46041</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>46245</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>46044</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>45798</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>46287</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45895</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>46133</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>45792</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>45800</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>45803</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>45803</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         <v>45803</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>45273</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>46246</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>46246</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>46289</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>45720</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>46083</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>45964</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>45274</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>46289</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>46059</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>45812</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>45812</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>44656</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45812</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>45812</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>45817</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45817</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45582</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>45735</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45819</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>46076</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>45472</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>46253</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>45821</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>45823</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>45821</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>46076</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>46252</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>45727</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         <v>45723</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>45741</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>45741</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>45827</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>45727</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>46251</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27809,7 +27809,7 @@
         <v>46251</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27882,7 +27882,7 @@
         <v>45817</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>46295</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>45832</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>45832</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28174,7 +28174,7 @@
         <v>46085</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>46084</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>45937</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28393,7 +28393,7 @@
         <v>44577</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>46254</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28539,7 +28539,7 @@
         <v>45836</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>45836</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>46091</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>46090</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>45839</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28904,7 +28904,7 @@
         <v>45839</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
         <v>45546</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>46097</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29123,7 +29123,7 @@
         <v>46099</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         <v>45841</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>46099</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>45392</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>46254</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>44854</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29561,7 +29561,7 @@
         <v>45846</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>44949</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>44866</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44886</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>44886</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>44886</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29999,7 +29999,7 @@
         <v>46105</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>46104</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>46105</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>45294</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45294</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>45294</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>45483</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>45483</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>46301</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>46111</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>45294</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>45308</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>45392</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>45866</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>46260</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>46119</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>46260</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>44882</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>46303</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>46303</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>45612</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>46260</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>45610</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>46260</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>46260</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>45567</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>46260</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>46260</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32043,7 +32043,7 @@
         <v>45877</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>46132</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32189,7 +32189,7 @@
         <v>44964</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32262,7 +32262,7 @@
         <v>46128</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>46306</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>44900</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>44859</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32554,7 +32554,7 @@
         <v>46306</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32627,7 +32627,7 @@
         <v>44630</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>45321</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>45575</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>44858</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>46306</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32997,7 +32997,7 @@
         <v>44888</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>46308</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>46310</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>45855</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>45216</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33372,7 +33372,7 @@
         <v>46310</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>46267</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>46267</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33591,7 +33591,7 @@
         <v>44639</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33664,7 +33664,7 @@
         <v>45453</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>44538</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>44552</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>45176</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33961,7 +33961,7 @@
         <v>45098</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34034,7 +34034,7 @@
         <v>46268</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34107,7 +34107,7 @@
         <v>46147</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34180,7 +34180,7 @@
         <v>44964</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>46268</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>45863</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34399,7 +34399,7 @@
         <v>45855</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34472,7 +34472,7 @@
         <v>45798</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>44581</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>46268</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>45688</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>45819</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34837,7 +34837,7 @@
         <v>45953</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34910,7 +34910,7 @@
         <v>45104</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34983,7 +34983,7 @@
         <v>45805</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>45842</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>45870</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45212</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>44910</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>45870</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>45678</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>45968</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44941</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>46306</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35718,7 +35718,7 @@
         <v>45579</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>46140</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35864,7 +35864,7 @@
         <v>45547</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45294</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>46141</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>45593</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36156,7 +36156,7 @@
         <v>44897</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>45582</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>46272</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36375,7 +36375,7 @@
         <v>46136</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>46306</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45225</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>44748</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>45935</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36745,7 +36745,7 @@
         <v>46153</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36818,7 +36818,7 @@
         <v>46153</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         <v>44740</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36964,7 +36964,7 @@
         <v>46153</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37037,7 +37037,7 @@
         <v>46153</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37110,7 +37110,7 @@
         <v>46153</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37183,7 +37183,7 @@
         <v>46153</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>45015</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>46154</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37402,7 +37402,7 @@
         <v>46154</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>46113</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45343</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37626,7 +37626,7 @@
         <v>45456</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44746</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45337</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37845,7 +37845,7 @@
         <v>44958</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>45258</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>45356</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38069,7 +38069,7 @@
         <v>45603</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38142,7 +38142,7 @@
         <v>44959</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38215,7 +38215,7 @@
         <v>45058</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38288,7 +38288,7 @@
         <v>45611</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>45058</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38434,7 +38434,7 @@
         <v>45119</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>45638</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>44993</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38653,7 +38653,7 @@
         <v>45119</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38726,7 +38726,7 @@
         <v>45119</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>45103</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>45629</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>45629</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39018,7 +39018,7 @@
         <v>45629</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39091,7 +39091,7 @@
         <v>45119</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>45582</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>45204</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>45120</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39383,7 +39383,7 @@
         <v>45477</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>45225</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39529,7 +39529,7 @@
         <v>45510</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>45176</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45547</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>45273</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39821,7 +39821,7 @@
         <v>45113</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39894,7 +39894,7 @@
         <v>45202</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>45197</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45053</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>45168</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>44571</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>45085</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>45538</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>45044</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>44897</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45646</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40624,7 +40624,7 @@
         <v>45211</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>45096</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>44896</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40843,7 +40843,7 @@
         <v>45216</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40916,7 +40916,7 @@
         <v>45110</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>45771</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>45727</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>45097</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>45770</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>45099</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>44546</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41437,7 +41437,7 @@
         <v>45120</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41510,7 +41510,7 @@
         <v>45120</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41583,7 +41583,7 @@
         <v>45120</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41656,7 +41656,7 @@
         <v>45120</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>45329</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41802,7 +41802,7 @@
         <v>45271</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41875,7 +41875,7 @@
         <v>45772</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41948,7 +41948,7 @@
         <v>45462</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42021,7 +42021,7 @@
         <v>45062</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42094,7 +42094,7 @@
         <v>45545</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>45294</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42240,7 +42240,7 @@
         <v>44889</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42318,7 +42318,7 @@
         <v>45120</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42391,7 +42391,7 @@
         <v>45316</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42464,7 +42464,7 @@
         <v>45637</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>45593</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>45162</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42683,7 +42683,7 @@
         <v>45611</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42756,7 +42756,7 @@
         <v>45562</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42829,7 +42829,7 @@
         <v>44609</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42902,7 +42902,7 @@
         <v>45670</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45155</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43048,7 +43048,7 @@
         <v>44515</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>45119</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45629</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43267,7 +43267,7 @@
         <v>45217</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45196</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>44547</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45357</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>45054</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>45631</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43705,7 +43705,7 @@
         <v>45671</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>44644</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43851,7 +43851,7 @@
         <v>45472</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>45579</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43997,7 +43997,7 @@
         <v>45119</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>45432</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44143,7 +44143,7 @@
         <v>44639</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>45316</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>45196</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44362,7 +44362,7 @@
         <v>44564</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44435,7 +44435,7 @@
         <v>45190</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>45351</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45636</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>45231</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>45205</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44800,7 +44800,7 @@
         <v>45212</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44873,7 +44873,7 @@
         <v>45629</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>45148</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>45099</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45126</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>45119</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45238,7 +45238,7 @@
         <v>45119</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45311,7 +45311,7 @@
         <v>45685</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45384,7 +45384,7 @@
         <v>45516</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45457,7 +45457,7 @@
         <v>45741</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45530,7 +45530,7 @@
         <v>45264</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>45120</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>45240</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45302</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45827,7 +45827,7 @@
         <v>44704</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45749</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45973,7 +45973,7 @@
         <v>45239</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45315</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46119,7 +46119,7 @@
         <v>45186</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46192,7 +46192,7 @@
         <v>45233</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46265,7 +46265,7 @@
         <v>45758</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46338,7 +46338,7 @@
         <v>45268</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45756</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45289</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46557,7 +46557,7 @@
         <v>44804</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45321</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46708,7 +46708,7 @@
         <v>44839</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>45321</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46859,7 +46859,7 @@
         <v>45316</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45240</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47005,7 +47005,7 @@
         <v>44916</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>45294</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47151,7 +47151,7 @@
         <v>44897</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47224,7 +47224,7 @@
         <v>45321</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47302,7 +47302,7 @@
         <v>45189</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47375,7 +47375,7 @@
         <v>45548</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45588</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>45197</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45224</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47667,7 +47667,7 @@
         <v>45197</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47740,7 +47740,7 @@
         <v>45180</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>44964</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47886,7 +47886,7 @@
         <v>45215</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>44875</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48032,7 +48032,7 @@
         <v>45561</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48105,7 +48105,7 @@
         <v>45462</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48178,7 +48178,7 @@
         <v>44914</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45769</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48324,7 +48324,7 @@
         <v>44900</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48397,7 +48397,7 @@
         <v>45015</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48470,7 +48470,7 @@
         <v>44995</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>44592</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48616,7 +48616,7 @@
         <v>44624</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>44642</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48762,7 +48762,7 @@
         <v>45513</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>44706</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48913,7 +48913,7 @@
         <v>45174</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48986,7 +48986,7 @@
         <v>44785</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>45008</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49132,7 +49132,7 @@
         <v>44900</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49205,7 +49205,7 @@
         <v>44865</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49278,7 +49278,7 @@
         <v>45257</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>45173</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49424,7 +49424,7 @@
         <v>44900</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49497,7 +49497,7 @@
         <v>45173</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49570,7 +49570,7 @@
         <v>44900</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49643,7 +49643,7 @@
         <v>45534</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49716,7 +49716,7 @@
         <v>45814</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49789,7 +49789,7 @@
         <v>45429</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49862,7 +49862,7 @@
         <v>45831</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49935,7 +49935,7 @@
         <v>45890</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>45979</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50081,7 +50081,7 @@
         <v>45740</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>45740</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         <v>45127</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50300,7 +50300,7 @@
         <v>46073</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50373,7 +50373,7 @@
         <v>46083</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>

--- a/Översikt BORÅS.xlsx
+++ b/Översikt BORÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45471</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>45210</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>45671</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45435</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45943</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>45187</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>46042</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45321</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44624</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45204</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>45393</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>44501</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>45526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>44873</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>44721</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>45944</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>45316</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>45982</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>45393</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>45629</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>45604</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>46076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>46308</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>44748</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>44546</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>45275</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45351</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>44691</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>44817</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>45140</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>44949</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>45379</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>46052</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>45846</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>45867</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>44630</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>45119</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>45093</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>44589</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>45153</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>45153</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44750</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>45281</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>45007</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>44873</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45348</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>44824</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>45867</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>44544</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>45267</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>44879</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>45260</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>45510</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>45943</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>44958</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>44742</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>46198</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>45686</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>45629</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>46008</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>46280</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>45793</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         <v>45793</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>45826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>45841</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>46259</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>45321</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>44750</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>45321</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>45126</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>45321</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>45671</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>45240</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>45264</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>44873</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>45671</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>46104</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>44586</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         <v>44512</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44656</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>44631</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>44617</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>44683</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>44544</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>44830</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>44538</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>44817</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>44817</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>44734</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>44837</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>44586</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>44873</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>44538</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>44510</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>44511</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>44544</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>44887</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>44502</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>44523</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>44511</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>44606</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>44605</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>44845</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>44845</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>44624</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
         <v>44845</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>44769</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44673</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>44753</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>44873</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>44565</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>44550</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>44882</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>44529</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>44642</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>44505</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>44678</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>45048</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>45887</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>45646</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>45888</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>45888</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         <v>45301</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>44771</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>45546</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>45888</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>45412</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>45050</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>45888</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>45593</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>45194</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45308</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44656</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>45308</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>45350</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>44844</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>45670</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>45210</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>45406</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>45909</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>45909</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44987</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44825</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>45510</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>44958</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>44652</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>45678</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45917</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>45922</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45922</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45924</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>45925</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>44992</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45917</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>45929</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>45931</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45120</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45120</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45845</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45364</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>45931</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>45000</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45931</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>44848</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>45472</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>45525</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>45050</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>45050</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>45938</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>46175</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45264</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45803</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45943</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>45120</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>46176</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>45650</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45937</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>44958</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>44916</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44958</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45538</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45119</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>45947</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>45947</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>46183</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>46183</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45184</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45666</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>46182</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>45421</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>46183</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>44728</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45953</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45960</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45959</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>45126</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45951</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>45194</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         <v>46184</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>45629</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>46184</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>45119</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>45961</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>46188</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>45961</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>45119</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>44866</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>45232</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>45537</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>45412</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>46198</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>46198</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>45440</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>45205</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>45974</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45240</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>44980</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>46198</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>45379</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>46183</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>46203</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>45034</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>46202</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>45982</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>45982</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>46203</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>45982</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>46204</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>46204</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45062</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>46204</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>44914</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>45268</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>45985</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>45211</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>45321</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
         <v>45208</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20995,7 +20995,7 @@
         <v>46204</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>46206</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>45762</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45988</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>45992</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45119</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45632</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>45989</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>45994</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45994</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>45474</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>45996</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>46217</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>46216</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>46216</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>45776</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45782</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>46224</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22319,7 +22319,7 @@
         <v>45475</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>45587</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>45784</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>45783</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>46008</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45783</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>46008</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>44837</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45596</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>45721</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>45209</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45688</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45615</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>45701</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>45713</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45715</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>45688</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>45699</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>46280</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>45789</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>45789</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>45726</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>45142</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>46035</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>46036</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>46036</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>46037</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>46037</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24368,7 +24368,7 @@
         <v>46041</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>46245</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>46044</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>45798</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>46287</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45895</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>46133</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>45792</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>45800</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>45803</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>45803</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         <v>45803</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>45273</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>46246</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>46246</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>46289</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>45720</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>46083</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>45964</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>45274</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>46289</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>46059</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>45812</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>45812</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>44656</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45812</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>45812</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>45817</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45817</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45582</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>45735</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45819</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>46076</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>45472</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>46253</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>45821</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>45823</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>45821</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>46076</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>46252</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>45727</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         <v>45723</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>45741</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>45741</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>45827</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>45727</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>46251</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27809,7 +27809,7 @@
         <v>46251</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27882,7 +27882,7 @@
         <v>45817</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>46295</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>45832</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>45832</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28174,7 +28174,7 @@
         <v>46085</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>46084</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>45937</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28393,7 +28393,7 @@
         <v>44577</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>46254</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28539,7 +28539,7 @@
         <v>45836</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>45836</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>46091</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>46090</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>45839</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28904,7 +28904,7 @@
         <v>45839</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
         <v>45546</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>46097</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29123,7 +29123,7 @@
         <v>46099</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         <v>45841</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>46099</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>45392</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>46254</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>44854</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29561,7 +29561,7 @@
         <v>45846</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>44949</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>44866</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44886</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>44886</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>44886</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29999,7 +29999,7 @@
         <v>46105</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>46104</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>46105</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>45294</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45294</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>45294</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>45483</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>45483</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>46301</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>46111</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>45294</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>45308</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>45392</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>45866</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>46260</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>46119</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>46260</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>44882</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>46303</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>46303</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>45612</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>46260</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>45610</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>46260</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>46260</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>45567</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>46260</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>46260</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32043,7 +32043,7 @@
         <v>45877</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>46132</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32189,7 +32189,7 @@
         <v>44964</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32262,7 +32262,7 @@
         <v>46128</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>46306</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32408,7 +32408,7 @@
         <v>44900</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>44859</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32554,7 +32554,7 @@
         <v>46306</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32627,7 +32627,7 @@
         <v>44630</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>45321</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>45575</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>44858</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>46306</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32997,7 +32997,7 @@
         <v>44888</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>46308</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>46310</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>45855</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>45216</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33372,7 +33372,7 @@
         <v>46310</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>46267</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>46267</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33591,7 +33591,7 @@
         <v>44639</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33664,7 +33664,7 @@
         <v>45453</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>44538</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>44552</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>45176</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33961,7 +33961,7 @@
         <v>45098</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34034,7 +34034,7 @@
         <v>46268</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34107,7 +34107,7 @@
         <v>46147</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34180,7 +34180,7 @@
         <v>44964</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>46268</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>45863</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34399,7 +34399,7 @@
         <v>45855</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34472,7 +34472,7 @@
         <v>45798</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>44581</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>46268</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>45688</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>45819</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34837,7 +34837,7 @@
         <v>45953</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34910,7 +34910,7 @@
         <v>45104</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34983,7 +34983,7 @@
         <v>45805</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>45842</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>45870</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45212</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>44910</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>45870</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>45678</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>45968</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44941</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>46306</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35718,7 +35718,7 @@
         <v>45579</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>46140</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35864,7 +35864,7 @@
         <v>45547</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45294</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>46141</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>45593</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36156,7 +36156,7 @@
         <v>44897</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>45582</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>46272</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36375,7 +36375,7 @@
         <v>46136</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>46306</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45225</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>44748</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>45935</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36745,7 +36745,7 @@
         <v>46153</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36818,7 +36818,7 @@
         <v>46153</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         <v>44740</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36964,7 +36964,7 @@
         <v>46153</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37037,7 +37037,7 @@
         <v>46153</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37110,7 +37110,7 @@
         <v>46153</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37183,7 +37183,7 @@
         <v>46153</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>45015</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>46154</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37402,7 +37402,7 @@
         <v>46154</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>46113</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45343</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37626,7 +37626,7 @@
         <v>45456</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44746</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45337</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37845,7 +37845,7 @@
         <v>44958</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>45258</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>45356</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38069,7 +38069,7 @@
         <v>45603</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38142,7 +38142,7 @@
         <v>44959</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38215,7 +38215,7 @@
         <v>45058</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38288,7 +38288,7 @@
         <v>45611</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>45058</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38434,7 +38434,7 @@
         <v>45119</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>45638</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38580,7 +38580,7 @@
         <v>44993</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38653,7 +38653,7 @@
         <v>45119</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38726,7 +38726,7 @@
         <v>45119</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>45103</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>45629</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>45629</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39018,7 +39018,7 @@
         <v>45629</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39091,7 +39091,7 @@
         <v>45119</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>45582</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>45204</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>45120</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39383,7 +39383,7 @@
         <v>45477</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>45225</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39529,7 +39529,7 @@
         <v>45510</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>45176</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>45547</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>45273</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39821,7 +39821,7 @@
         <v>45113</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39894,7 +39894,7 @@
         <v>45202</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>45197</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45053</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>45168</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>44571</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>45085</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>45538</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>45044</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>44897</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45646</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40624,7 +40624,7 @@
         <v>45211</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>45096</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>44896</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40843,7 +40843,7 @@
         <v>45216</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40916,7 +40916,7 @@
         <v>45110</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>45771</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>45727</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>45097</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>45770</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>45099</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>44546</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41437,7 +41437,7 @@
         <v>45120</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41510,7 +41510,7 @@
         <v>45120</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41583,7 +41583,7 @@
         <v>45120</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41656,7 +41656,7 @@
         <v>45120</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>45329</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41802,7 +41802,7 @@
         <v>45271</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41875,7 +41875,7 @@
         <v>45772</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41948,7 +41948,7 @@
         <v>45462</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42021,7 +42021,7 @@
         <v>45062</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42094,7 +42094,7 @@
         <v>45545</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>45294</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42240,7 +42240,7 @@
         <v>44889</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42318,7 +42318,7 @@
         <v>45120</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42391,7 +42391,7 @@
         <v>45316</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42464,7 +42464,7 @@
         <v>45637</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>45593</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>45162</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42683,7 +42683,7 @@
         <v>45611</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42756,7 +42756,7 @@
         <v>45562</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42829,7 +42829,7 @@
         <v>44609</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42902,7 +42902,7 @@
         <v>45670</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45155</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43048,7 +43048,7 @@
         <v>44515</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>45119</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45629</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43267,7 +43267,7 @@
         <v>45217</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45196</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>44547</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43486,7 +43486,7 @@
         <v>45357</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>45054</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>45631</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43705,7 +43705,7 @@
         <v>45671</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>44644</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43851,7 +43851,7 @@
         <v>45472</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43924,7 +43924,7 @@
         <v>45579</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43997,7 +43997,7 @@
         <v>45119</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>45432</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44143,7 +44143,7 @@
         <v>44639</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>45316</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>45196</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44362,7 +44362,7 @@
         <v>44564</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44435,7 +44435,7 @@
         <v>45190</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>45351</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45636</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>45231</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>45205</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44800,7 +44800,7 @@
         <v>45212</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44873,7 +44873,7 @@
         <v>45629</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>45148</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>45099</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45092,7 +45092,7 @@
         <v>45126</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>45119</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45238,7 +45238,7 @@
         <v>45119</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45311,7 +45311,7 @@
         <v>45685</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45384,7 +45384,7 @@
         <v>45516</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45457,7 +45457,7 @@
         <v>45741</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45530,7 +45530,7 @@
         <v>45264</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45603,7 +45603,7 @@
         <v>45120</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>45240</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>45302</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45827,7 +45827,7 @@
         <v>44704</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45749</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45973,7 +45973,7 @@
         <v>45239</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45315</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46119,7 +46119,7 @@
         <v>45186</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46192,7 +46192,7 @@
         <v>45233</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46265,7 +46265,7 @@
         <v>45758</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46338,7 +46338,7 @@
         <v>45268</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>45756</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45289</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46557,7 +46557,7 @@
         <v>44804</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45321</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46708,7 +46708,7 @@
         <v>44839</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>45321</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46859,7 +46859,7 @@
         <v>45316</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45240</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47005,7 +47005,7 @@
         <v>44916</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>45294</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47151,7 +47151,7 @@
         <v>44897</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47224,7 +47224,7 @@
         <v>45321</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47302,7 +47302,7 @@
         <v>45189</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47375,7 +47375,7 @@
         <v>45548</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45588</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>45197</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45224</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47667,7 +47667,7 @@
         <v>45197</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47740,7 +47740,7 @@
         <v>45180</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>44964</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47886,7 +47886,7 @@
         <v>45215</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>44875</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48032,7 +48032,7 @@
         <v>45561</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48105,7 +48105,7 @@
         <v>45462</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48178,7 +48178,7 @@
         <v>44914</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45769</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48324,7 +48324,7 @@
         <v>44900</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48397,7 +48397,7 @@
         <v>45015</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48470,7 +48470,7 @@
         <v>44995</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>44592</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48616,7 +48616,7 @@
         <v>44624</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>44642</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48762,7 +48762,7 @@
         <v>45513</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>44706</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48913,7 +48913,7 @@
         <v>45174</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48986,7 +48986,7 @@
         <v>44785</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>45008</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49132,7 +49132,7 @@
         <v>44900</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49205,7 +49205,7 @@
         <v>44865</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49278,7 +49278,7 @@
         <v>45257</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>45173</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49424,7 +49424,7 @@
         <v>44900</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49497,7 +49497,7 @@
         <v>45173</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49570,7 +49570,7 @@
         <v>44900</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49643,7 +49643,7 @@
         <v>45534</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49716,7 +49716,7 @@
         <v>45814</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49789,7 +49789,7 @@
         <v>45429</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49862,7 +49862,7 @@
         <v>45831</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49935,7 +49935,7 @@
         <v>45890</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>45979</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50081,7 +50081,7 @@
         <v>45740</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>45740</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         <v>45127</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50300,7 +50300,7 @@
         <v>46073</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50373,7 +50373,7 @@
         <v>46083</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
